--- a/data/merged/2026-08-31/MERGED_UK_Spot-Cleaner_2026-08-31.xlsx
+++ b/data/merged/2026-08-31/MERGED_UK_Spot-Cleaner_2026-08-31.xlsx
@@ -4129,7 +4129,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -10714,40 +10714,40 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0FNX6YLCJ</t>
+          <t>B01MSJEGL8</t>
         </is>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Russell Hobbs</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0FNX6YLCJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/RussellHobbs/page/DBC20DE0-0B1A-4442-8FF1-4D12520F0C8F?lp_asin=B01MSJEGL8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Shark StainForce Dual-Formula Refill Cartridge, 2 x 500ml XSKBDHXCM500UKsValue 2-pack, formulated to tackle tough stains an</t>
+          <t>Russell Hobbs RHCC5001 Lightweight 600w Carpet Washer &amp; Cleaner White &amp; Aqua</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FNX6YLCJ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B01MSJEGL8?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71SuXoGPIQL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61wQefXoNXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0FNX6YLCJ</t>
+          <t>B01MSJEGL8</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -10761,13 +10761,13 @@
         </is>
       </c>
       <c r="O29" s="15">
-        <v>5809</v>
+        <v>7642</v>
       </c>
       <c r="P29" s="15">
-        <v>-1403</v>
+        <v>18104</v>
       </c>
       <c r="Q29" s="16">
-        <v>-0.32</v>
+        <v>0.7</v>
       </c>
       <c r="R29" s="17" t="inlineStr">
         <is>
@@ -10776,61 +10776,63 @@
       </c>
       <c r="S29" s="18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="T29" s="15">
-        <v>874</v>
+        <v>376</v>
       </c>
       <c r="U29" s="16">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="V29" s="15">
-        <v>26211</v>
+        <v>25568</v>
       </c>
       <c r="W29" s="15" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>300</t>
         </is>
       </c>
       <c r="X29" s="15">
-        <v>21112</v>
+        <v>20733</v>
       </c>
       <c r="Y29" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z29" s="20">
-        <v>29.99</v>
+        <v>56.67</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
-      <c r="AC29" s="15"/>
+      <c r="AC29" s="15">
+        <v>34</v>
+      </c>
       <c r="AD29" s="19">
-        <v>60</v>
+        <v>1003</v>
       </c>
       <c r="AE29" s="15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AF29" s="21">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AG29" s="22">
-        <v>0.0092</v>
+        <v>0</v>
       </c>
       <c r="AH29" s="20">
-        <v>3.1</v>
+        <v>7.31</v>
       </c>
       <c r="AI29" s="16">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="13" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2016-12-07</t>
         </is>
       </c>
       <c r="AL29" s="19">
-        <v>356</v>
+        <v>3553</v>
       </c>
       <c r="AM29" s="13" t="inlineStr">
         <is>
@@ -10841,10 +10843,10 @@
       <c r="AO29" s="13"/>
       <c r="AP29"/>
       <c r="AQ29" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR29" s="19">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AS29" s="14" t="inlineStr">
         <is>
@@ -10889,47 +10891,47 @@
       </c>
       <c r="BJ29" s="23" t="inlineStr">
         <is>
-          <t>1.3 kg</t>
+          <t>5.8 kg</t>
         </is>
       </c>
       <c r="BK29" s="23" t="inlineStr">
         <is>
-          <t>1.30 kg</t>
+          <t>5.80 kg</t>
         </is>
       </c>
       <c r="BL29" s="23" t="inlineStr">
         <is>
-          <t>15.7 x 15.5 x 10.8 cm</t>
+          <t>28.5 x 73.5 x 45.5 cm</t>
         </is>
       </c>
       <c r="BM29" s="23" t="inlineStr">
         <is>
-          <t>15.70 x 15.50 x 10.80 cm</t>
+          <t>28.50 x 73.50 x 45.50 cm</t>
         </is>
       </c>
       <c r="BN29" s="23" t="inlineStr">
         <is>
-          <t>1.34 kg</t>
+          <t>9.08 kg</t>
         </is>
       </c>
       <c r="BO29" s="23" t="inlineStr">
         <is>
-          <t>1.34 kg</t>
+          <t>9.08 kg</t>
         </is>
       </c>
       <c r="BP29" s="23" t="inlineStr">
         <is>
-          <t>16 x 15.5 x 11.1 cm</t>
+          <t>73.4 x 45.4 x 29 cm</t>
         </is>
       </c>
       <c r="BQ29" s="23" t="inlineStr">
         <is>
-          <t>16.00 x 15.50 x 11.10 cm</t>
+          <t>73.40 x 45.40 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR29" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -10940,40 +10942,40 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B01MSJEGL8</t>
+          <t>B0DSZVCZ6P</t>
         </is>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>Russell Hobbs</t>
+          <t>Hjh</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/RussellHobbs/page/DBC20DE0-0B1A-4442-8FF1-4D12520F0C8F?lp_asin=B01MSJEGL8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Hjh</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Russell Hobbs RHCC5001 Lightweight 600w Carpet Washer &amp; Cleaner White &amp; Aqua</t>
+          <t>Carpet Cleaner &amp; Spot Cleaner, Handheld Carpet Cleaner MachinessUpholstery Cleaner | Clean Up Spills &amp; Pet Messes from Carp</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B01MSJEGL8?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61wQefXoNXL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B01MSJEGL8</t>
+          <t>B0DSZVCZ6P</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -10987,13 +10989,13 @@
         </is>
       </c>
       <c r="O30" s="15">
-        <v>7642</v>
+        <v>18972</v>
       </c>
       <c r="P30" s="15">
-        <v>18104</v>
+        <v>-568</v>
       </c>
       <c r="Q30" s="16">
-        <v>0.7</v>
+        <v>-0.03</v>
       </c>
       <c r="R30" s="17" t="inlineStr">
         <is>
@@ -11002,91 +11004,101 @@
       </c>
       <c r="S30" s="18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T30" s="15">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="U30" s="16">
-        <v>-0.2</v>
+        <v>-0.42</v>
       </c>
       <c r="V30" s="15">
-        <v>25568</v>
+        <v>20174</v>
       </c>
       <c r="W30" s="15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X30" s="15">
-        <v>20733</v>
+        <v>11398</v>
       </c>
       <c r="Y30" s="19">
         <v>3</v>
       </c>
       <c r="Z30" s="20">
-        <v>56.67</v>
+        <v>56.99</v>
       </c>
       <c r="AA30"/>
       <c r="AB30"/>
-      <c r="AC30" s="15">
-        <v>34</v>
-      </c>
+      <c r="AC30" s="15"/>
       <c r="AD30" s="19">
-        <v>1003</v>
+        <v>340</v>
       </c>
       <c r="AE30" s="15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AF30" s="21">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG30" s="22">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
       <c r="AH30" s="20">
-        <v>7.31</v>
+        <v>3.43</v>
       </c>
       <c r="AI30" s="16">
-        <v>0.89</v>
+        <v>0.94</v>
       </c>
       <c r="AJ30"/>
       <c r="AK30" s="13" t="inlineStr">
         <is>
-          <t>2016-12-07</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AL30" s="19">
-        <v>3553</v>
+        <v>566</v>
       </c>
       <c r="AM30" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN30" s="13"/>
       <c r="AO30" s="13"/>
       <c r="AP30"/>
       <c r="AQ30" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR30" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS30" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>penmingkeji</t>
         </is>
       </c>
       <c r="AT30" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU30" s="13"/>
-      <c r="AV30" s="14"/>
-      <c r="AW30" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU30" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV30" s="14" t="inlineStr">
+        <is>
+          <t>安庆市 安徽 246000 CN</t>
+        </is>
+      </c>
+      <c r="AW30" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UO155PK9MELH</t>
+        </is>
+      </c>
       <c r="AX30" s="13"/>
       <c r="AY30" s="13" t="inlineStr">
         <is>
@@ -11117,47 +11129,47 @@
       </c>
       <c r="BJ30" s="23" t="inlineStr">
         <is>
-          <t>5.8 kg</t>
+          <t>4.3 kg</t>
         </is>
       </c>
       <c r="BK30" s="23" t="inlineStr">
         <is>
-          <t>5.80 kg</t>
+          <t>4.30 kg</t>
         </is>
       </c>
       <c r="BL30" s="23" t="inlineStr">
         <is>
-          <t>28.5 x 73.5 x 45.5 cm</t>
+          <t>44 x 33.9 x 19.7 cm</t>
         </is>
       </c>
       <c r="BM30" s="23" t="inlineStr">
         <is>
-          <t>28.50 x 73.50 x 45.50 cm</t>
+          <t>44.00 x 33.90 x 19.70 cm</t>
         </is>
       </c>
       <c r="BN30" s="23" t="inlineStr">
         <is>
-          <t>9.08 kg</t>
+          <t>4.74 kg</t>
         </is>
       </c>
       <c r="BO30" s="23" t="inlineStr">
         <is>
-          <t>9.08 kg</t>
+          <t>4.74 kg</t>
         </is>
       </c>
       <c r="BP30" s="23" t="inlineStr">
         <is>
-          <t>73.4 x 45.4 x 29 cm</t>
+          <t>44.8 x 33.8 x 19.2 cm</t>
         </is>
       </c>
       <c r="BQ30" s="23" t="inlineStr">
         <is>
-          <t>73.40 x 45.40 x 29.00 cm</t>
+          <t>44.80 x 33.80 x 19.20 cm</t>
         </is>
       </c>
       <c r="BR30" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -11168,40 +11180,40 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0DSZVCZ6P</t>
+          <t>B0GGJB2H1M</t>
         </is>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Hjh</t>
+          <t>Olsen &amp;amp; Smith</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Hjh</t>
+          <t>https://www.amazon.co.uk/stores/OlsenSmith/page/1FA1F547-221C-40C6-BA4F-6E13B39F7CE1?lp_asin=B0GGJB2H1M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Carpet Cleaner &amp; Spot Cleaner, Handheld Carpet Cleaner MachinessUpholstery Cleaner | Clean Up Spills &amp; Pet Messes from Carp</t>
+          <t>Olsen &amp; Smith 1600W Dual-Tank Carpet &amp; Upholstrey Spot Cleaner, HandheldsCold, Warm &amp; Steam Stain Removal, Upholstery Clean</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GGJB2H1M?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/719P6ABoSnL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0DSZVCZ6P</t>
+          <t>B0GGJB2H1M</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -11215,13 +11227,13 @@
         </is>
       </c>
       <c r="O31" s="15">
-        <v>18972</v>
+        <v>32897</v>
       </c>
       <c r="P31" s="15">
-        <v>-568</v>
+        <v>-11570</v>
       </c>
       <c r="Q31" s="16">
-        <v>-0.03</v>
+        <v>-0.54</v>
       </c>
       <c r="R31" s="17" t="inlineStr">
         <is>
@@ -11230,17 +11242,17 @@
       </c>
       <c r="S31" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T31" s="15">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="U31" s="16">
-        <v>-0.42</v>
+        <v>-0.21</v>
       </c>
       <c r="V31" s="15">
-        <v>20174</v>
+        <v>19035</v>
       </c>
       <c r="W31" s="15" t="inlineStr">
         <is>
@@ -11248,10 +11260,10 @@
         </is>
       </c>
       <c r="X31" s="15">
-        <v>11398</v>
+        <v>9456</v>
       </c>
       <c r="Y31" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z31" s="20">
         <v>56.99</v>
@@ -11260,77 +11272,73 @@
       <c r="AB31"/>
       <c r="AC31" s="15"/>
       <c r="AD31" s="19">
-        <v>340</v>
+        <v>67</v>
       </c>
       <c r="AE31" s="15">
         <v>8</v>
       </c>
       <c r="AF31" s="21">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AG31" s="22">
-        <v>0.0226</v>
+        <v>0.024</v>
       </c>
       <c r="AH31" s="20">
-        <v>3.43</v>
+        <v>5.48</v>
       </c>
       <c r="AI31" s="16">
-        <v>0.94</v>
+        <v>0.9</v>
       </c>
       <c r="AJ31"/>
       <c r="AK31" s="13" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="AL31" s="19">
-        <v>566</v>
+        <v>229</v>
       </c>
       <c r="AM31" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN31" s="13"/>
       <c r="AO31" s="13"/>
       <c r="AP31"/>
       <c r="AQ31" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR31" s="19">
         <v>1</v>
       </c>
       <c r="AS31" s="14" t="inlineStr">
         <is>
-          <t>penmingkeji</t>
+          <t>Travel Luggage &amp; Cabin Bags LTD</t>
         </is>
       </c>
       <c r="AT31" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU31" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV31" s="14" t="inlineStr">
         <is>
-          <t>安庆市 安徽 246000 CN</t>
+          <t>West Mids B73 6JR GB</t>
         </is>
       </c>
       <c r="AW31" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UO155PK9MELH</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3VYMLCCHTLVWV</t>
         </is>
       </c>
       <c r="AX31" s="13"/>
-      <c r="AY31" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY31" s="13"/>
       <c r="AZ31" s="13"/>
       <c r="BA31" s="13"/>
       <c r="BB31" s="13"/>
@@ -11348,54 +11356,50 @@
       <c r="BF31" s="13"/>
       <c r="BG31" s="13"/>
       <c r="BH31" s="14"/>
-      <c r="BI31" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI31" s="23"/>
       <c r="BJ31" s="23" t="inlineStr">
         <is>
-          <t>4.3 kg</t>
+          <t>5.2 kg</t>
         </is>
       </c>
       <c r="BK31" s="23" t="inlineStr">
         <is>
-          <t>4.30 kg</t>
+          <t>5.20 kg</t>
         </is>
       </c>
       <c r="BL31" s="23" t="inlineStr">
         <is>
-          <t>44 x 33.9 x 19.7 cm</t>
+          <t>35.4 x 34 x 31 cm</t>
         </is>
       </c>
       <c r="BM31" s="23" t="inlineStr">
         <is>
-          <t>44.00 x 33.90 x 19.70 cm</t>
+          <t>35.40 x 34.00 x 31.00 cm</t>
         </is>
       </c>
       <c r="BN31" s="23" t="inlineStr">
         <is>
-          <t>4.74 kg</t>
+          <t>6.9 kg</t>
         </is>
       </c>
       <c r="BO31" s="23" t="inlineStr">
         <is>
-          <t>4.74 kg</t>
+          <t>6.90 kg</t>
         </is>
       </c>
       <c r="BP31" s="23" t="inlineStr">
         <is>
-          <t>44.8 x 33.8 x 19.2 cm</t>
+          <t>35.4 x 34 x 31 cm</t>
         </is>
       </c>
       <c r="BQ31" s="23" t="inlineStr">
         <is>
-          <t>44.80 x 33.80 x 19.20 cm</t>
+          <t>35.40 x 34.00 x 31.00 cm</t>
         </is>
       </c>
       <c r="BR31" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -11406,40 +11410,40 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GGJB2H1M</t>
+          <t>B0H8Y31Y7C</t>
         </is>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Olsen &amp;amp; Smith</t>
+          <t>PUREBEAR</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/OlsenSmith/page/1FA1F547-221C-40C6-BA4F-6E13B39F7CE1?lp_asin=B0GGJB2H1M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/24-hourrapidresponse/page/2AA9E9E0-E703-4ECF-AC64-366A67AE77A7?lp_asin=B0H8Y31Y7C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Olsen &amp; Smith 1600W Dual-Tank Carpet &amp; Upholstrey Spot Cleaner, HandheldsCold, Warm &amp; Steam Stain Removal, Upholstery Clean</t>
+          <t>PUREBEAR Portable HandHeld Carpet Cleaner Machine, Spot Cleaners18Kpa Suction Power| Dual Tank| Upholstery| Stains, Couch,</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GGJB2H1M?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H8Y31Y7C?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/719P6ABoSnL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/614JtpGJI8L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GGJB2H1M</t>
+          <t>B0H8Y31Y7C</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -11453,13 +11457,13 @@
         </is>
       </c>
       <c r="O32" s="15">
-        <v>32897</v>
+        <v>13654</v>
       </c>
       <c r="P32" s="15">
-        <v>-11570</v>
+        <v>-1234</v>
       </c>
       <c r="Q32" s="16">
-        <v>-0.54</v>
+        <v>-0.1</v>
       </c>
       <c r="R32" s="17" t="inlineStr">
         <is>
@@ -11468,17 +11472,15 @@
       </c>
       <c r="S32" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>23</t>
         </is>
       </c>
       <c r="T32" s="15">
-        <v>334</v>
-      </c>
-      <c r="U32" s="16">
-        <v>-0.21</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="U32" s="16"/>
       <c r="V32" s="15">
-        <v>19035</v>
+        <v>17750</v>
       </c>
       <c r="W32" s="15" t="inlineStr">
         <is>
@@ -11486,85 +11488,89 @@
         </is>
       </c>
       <c r="X32" s="15">
-        <v>9456</v>
+        <v>15096</v>
       </c>
       <c r="Y32" s="19">
         <v>1</v>
       </c>
       <c r="Z32" s="20">
-        <v>56.99</v>
+        <v>66.48</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="15"/>
       <c r="AD32" s="19">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="AE32" s="15">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AF32" s="21">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AG32" s="22">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="AH32" s="20">
-        <v>5.48</v>
+        <v>5.33</v>
       </c>
       <c r="AI32" s="16">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="AJ32"/>
       <c r="AK32" s="13" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="AL32" s="19">
-        <v>229</v>
+        <v>46</v>
       </c>
       <c r="AM32" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN32" s="13"/>
       <c r="AO32" s="13"/>
       <c r="AP32"/>
       <c r="AQ32" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR32" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS32" s="14" t="inlineStr">
         <is>
-          <t>Travel Luggage &amp; Cabin Bags LTD</t>
+          <t>Xinhua County Hongxu Trading Co., Ltd</t>
         </is>
       </c>
       <c r="AT32" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU32" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV32" s="14" t="inlineStr">
         <is>
-          <t>West Mids B73 6JR GB</t>
+          <t>hunansheng 417600 CN</t>
         </is>
       </c>
       <c r="AW32" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3VYMLCCHTLVWV</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABDQMGK4MGMOL</t>
         </is>
       </c>
       <c r="AX32" s="13"/>
-      <c r="AY32" s="13"/>
+      <c r="AY32" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ32" s="13"/>
       <c r="BA32" s="13"/>
       <c r="BB32" s="13"/>
@@ -11582,45 +11588,41 @@
       <c r="BF32" s="13"/>
       <c r="BG32" s="13"/>
       <c r="BH32" s="14"/>
-      <c r="BI32" s="23"/>
+      <c r="BI32" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ32" s="23" t="inlineStr">
         <is>
-          <t>5.2 kg</t>
+          <t>4.16 kg</t>
         </is>
       </c>
       <c r="BK32" s="23" t="inlineStr">
         <is>
-          <t>5.20 kg</t>
-        </is>
-      </c>
-      <c r="BL32" s="23" t="inlineStr">
-        <is>
-          <t>35.4 x 34 x 31 cm</t>
-        </is>
-      </c>
-      <c r="BM32" s="23" t="inlineStr">
-        <is>
-          <t>35.40 x 34.00 x 31.00 cm</t>
-        </is>
-      </c>
+          <t>4.16 kg</t>
+        </is>
+      </c>
+      <c r="BL32" s="23"/>
+      <c r="BM32" s="23"/>
       <c r="BN32" s="23" t="inlineStr">
         <is>
-          <t>6.9 kg</t>
+          <t>4.16 kg</t>
         </is>
       </c>
       <c r="BO32" s="23" t="inlineStr">
         <is>
-          <t>6.90 kg</t>
+          <t>4.16 kg</t>
         </is>
       </c>
       <c r="BP32" s="23" t="inlineStr">
         <is>
-          <t>35.4 x 34 x 31 cm</t>
+          <t>41.9 x 35.6 x 20.8 cm</t>
         </is>
       </c>
       <c r="BQ32" s="23" t="inlineStr">
         <is>
-          <t>35.40 x 34.00 x 31.00 cm</t>
+          <t>41.90 x 35.60 x 20.80 cm</t>
         </is>
       </c>
       <c r="BR32" s="13" t="inlineStr">
@@ -11636,40 +11638,40 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0H8Y31Y7C</t>
+          <t>B0FXGBT4LF</t>
         </is>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>PUREBEAR</t>
+          <t>Domixo</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/24-hourrapidresponse/page/2AA9E9E0-E703-4ECF-AC64-366A67AE77A7?lp_asin=B0H8Y31Y7C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Domixo</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>PUREBEAR Portable HandHeld Carpet Cleaner Machine, Spot Cleaners18Kpa Suction Power| Dual Tank| Upholstery| Stains, Couch,</t>
+          <t>Domixo Carpet Cleaner Machines, Hot Water Multi-Purpose Portable Spot Cleaner, Wet/dry Upholstery Cleaner, 450W &amp; Touchscreen</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H8Y31Y7C?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FXGBT4LF?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/614JtpGJI8L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71NkpfFNvkL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0H8Y31Y7C</t>
+          <t>B0FXGBT4LF</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
@@ -11683,13 +11685,13 @@
         </is>
       </c>
       <c r="O33" s="15">
-        <v>13654</v>
+        <v>37296</v>
       </c>
       <c r="P33" s="15">
-        <v>-1234</v>
+        <v>-8701</v>
       </c>
       <c r="Q33" s="16">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="R33" s="17" t="inlineStr">
         <is>
@@ -11698,59 +11700,61 @@
       </c>
       <c r="S33" s="18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T33" s="15">
-        <v>267</v>
-      </c>
-      <c r="U33" s="16"/>
+        <v>195</v>
+      </c>
+      <c r="U33" s="16">
+        <v>0.8</v>
+      </c>
       <c r="V33" s="15">
-        <v>17750</v>
+        <v>13648</v>
       </c>
       <c r="W33" s="15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X33" s="15">
-        <v>15096</v>
+        <v>6753</v>
       </c>
       <c r="Y33" s="19">
         <v>1</v>
       </c>
       <c r="Z33" s="20">
-        <v>66.48</v>
+        <v>69.99</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
       <c r="AC33" s="15"/>
       <c r="AD33" s="19">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="AE33" s="15">
         <v>0</v>
       </c>
       <c r="AF33" s="21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
       </c>
       <c r="AH33" s="20">
-        <v>5.33</v>
+        <v>3.43</v>
       </c>
       <c r="AI33" s="16">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AJ33"/>
       <c r="AK33" s="13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AL33" s="19">
-        <v>46</v>
+        <v>297</v>
       </c>
       <c r="AM33" s="13" t="inlineStr">
         <is>
@@ -11764,11 +11768,11 @@
         <v>10</v>
       </c>
       <c r="AR33" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS33" s="14" t="inlineStr">
         <is>
-          <t>Xinhua County Hongxu Trading Co., Ltd</t>
+          <t>qingziyu58</t>
         </is>
       </c>
       <c r="AT33" s="13" t="inlineStr">
@@ -11783,12 +11787,12 @@
       </c>
       <c r="AV33" s="14" t="inlineStr">
         <is>
-          <t>hunansheng 417600 CN</t>
+          <t>广州市 广东 510080 CN</t>
         </is>
       </c>
       <c r="AW33" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABDQMGK4MGMOL</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WYJ2QAIMP7S0</t>
         </is>
       </c>
       <c r="AX33" s="13"/>
@@ -11821,39 +11825,47 @@
       </c>
       <c r="BJ33" s="23" t="inlineStr">
         <is>
-          <t>4.16 kg</t>
+          <t>4.61 kg</t>
         </is>
       </c>
       <c r="BK33" s="23" t="inlineStr">
         <is>
-          <t>4.16 kg</t>
-        </is>
-      </c>
-      <c r="BL33" s="23"/>
-      <c r="BM33" s="23"/>
+          <t>4.61 kg</t>
+        </is>
+      </c>
+      <c r="BL33" s="23" t="inlineStr">
+        <is>
+          <t>19.4 x 33.4 x 44.4 cm</t>
+        </is>
+      </c>
+      <c r="BM33" s="23" t="inlineStr">
+        <is>
+          <t>19.40 x 33.40 x 44.40 cm</t>
+        </is>
+      </c>
       <c r="BN33" s="23" t="inlineStr">
         <is>
-          <t>4.16 kg</t>
+          <t>4.61 kg</t>
         </is>
       </c>
       <c r="BO33" s="23" t="inlineStr">
         <is>
-          <t>4.16 kg</t>
+          <t>4.61 kg</t>
         </is>
       </c>
       <c r="BP33" s="23" t="inlineStr">
         <is>
-          <t>41.9 x 35.6 x 20.8 cm</t>
+          <t>44.4 x 33.4 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ33" s="23" t="inlineStr">
         <is>
-          <t>41.90 x 35.60 x 20.80 cm</t>
+          <t>44.40 x 33.40 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR33" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -11864,40 +11876,40 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0FXGBT4LF</t>
+          <t>B0FWS2V14K</t>
         </is>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Domixo</t>
+          <t>ToyGem</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Domixo</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=ToyGem</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Domixo Carpet Cleaner Machines, Hot Water Multi-Purpose Portable Spot Cleaner, Wet/dry Upholstery Cleaner, 450W &amp; Touchscreen</t>
+          <t>Carpet Cleaner, Portable Spot Cleaner 600W, Pro 18Kpa Upholstery Cleaner to Remove Spills &amp; Pet Messes, Carpet Stain Remover</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FXGBT4LF?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FWS2V14K?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71NkpfFNvkL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51HxyFWy+ZL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0FXGBT4LF</t>
+          <t>B0FWS2V14K</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -11911,13 +11923,13 @@
         </is>
       </c>
       <c r="O34" s="15">
-        <v>37296</v>
+        <v>34368</v>
       </c>
       <c r="P34" s="15">
-        <v>-8701</v>
+        <v>-4299</v>
       </c>
       <c r="Q34" s="16">
-        <v>-0.3</v>
+        <v>-0.14</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -11926,17 +11938,17 @@
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T34" s="15">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="U34" s="16">
-        <v>0.8</v>
+        <v>-0.27</v>
       </c>
       <c r="V34" s="15">
-        <v>13648</v>
+        <v>12598</v>
       </c>
       <c r="W34" s="15" t="inlineStr">
         <is>
@@ -11944,10 +11956,10 @@
         </is>
       </c>
       <c r="X34" s="15">
-        <v>6753</v>
+        <v>7322</v>
       </c>
       <c r="Y34" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z34" s="20">
         <v>69.99</v>
@@ -11956,7 +11968,7 @@
       <c r="AB34"/>
       <c r="AC34" s="15"/>
       <c r="AD34" s="19">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="AE34" s="15">
         <v>0</v>
@@ -11968,19 +11980,19 @@
         <v>0</v>
       </c>
       <c r="AH34" s="20">
-        <v>3.43</v>
+        <v>5.18</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
@@ -11994,11 +12006,11 @@
         <v>10</v>
       </c>
       <c r="AR34" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>qingziyu58</t>
+          <t>GOTTSCHALL GALEN LTD</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
@@ -12008,17 +12020,17 @@
       </c>
       <c r="AU34" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV34" s="14" t="inlineStr">
         <is>
-          <t>广州市 广东 510080 CN</t>
+          <t>United Kingdom E16 2GP GB</t>
         </is>
       </c>
       <c r="AW34" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WYJ2QAIMP7S0</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2F8EA95F3IAV8</t>
         </is>
       </c>
       <c r="AX34" s="13"/>
@@ -12051,47 +12063,47 @@
       </c>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>4.61 kg</t>
+          <t>5.18 kg</t>
         </is>
       </c>
       <c r="BK34" s="23" t="inlineStr">
         <is>
-          <t>4.61 kg</t>
+          <t>5.18 kg</t>
         </is>
       </c>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>19.4 x 33.4 x 44.4 cm</t>
+          <t>39 x 35 x 20 cm</t>
         </is>
       </c>
       <c r="BM34" s="23" t="inlineStr">
         <is>
-          <t>19.40 x 33.40 x 44.40 cm</t>
+          <t>39.00 x 35.00 x 20.00 cm</t>
         </is>
       </c>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>4.61 kg</t>
+          <t>5.18 kg</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>4.61 kg</t>
+          <t>5.18 kg</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>44.4 x 33.4 x 19.4 cm</t>
+          <t>38.5 x 34.5 x 20.5 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>44.40 x 33.40 x 19.40 cm</t>
+          <t>38.50 x 34.50 x 20.50 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -12102,40 +12114,40 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0FWS2V14K</t>
+          <t>B096KMBG8K</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>ToyGem</t>
+          <t>VYTRONIX</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=ToyGem</t>
+          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B096KMBG8K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Carpet Cleaner, Portable Spot Cleaner 600W, Pro 18Kpa Upholstery Cleaner to Remove Spills &amp; Pet Messes, Carpet Stain Remover</t>
+          <t>VYTRONIX WSH60 Multi-Function Wet &amp; Dry Vacuum Cleaner &amp; Carpet CleanersPortable 4-in-1 Carpet Washer and Floor Cleaner wit</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FWS2V14K?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B096KMBG8K?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51HxyFWy+ZL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/415g5BMj1rL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0FWS2V14K</t>
+          <t>B096KMBG8K</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -12149,13 +12161,13 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>34368</v>
+        <v>106836</v>
       </c>
       <c r="P35" s="15">
-        <v>-4299</v>
+        <v>-37979</v>
       </c>
       <c r="Q35" s="16">
-        <v>-0.14</v>
+        <v>-0.55</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -12164,17 +12176,17 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T35" s="15">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="U35" s="16">
-        <v>-0.27</v>
+        <v>0.1</v>
       </c>
       <c r="V35" s="15">
-        <v>12598</v>
+        <v>11519</v>
       </c>
       <c r="W35" s="15" t="inlineStr">
         <is>
@@ -12182,31 +12194,33 @@
         </is>
       </c>
       <c r="X35" s="15">
-        <v>7322</v>
+        <v>7999</v>
       </c>
       <c r="Y35" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z35" s="20">
-        <v>69.99</v>
+        <v>79.99</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
-      <c r="AC35" s="15"/>
+      <c r="AC35" s="15">
+        <v>25</v>
+      </c>
       <c r="AD35" s="19">
-        <v>157</v>
+        <v>1189</v>
       </c>
       <c r="AE35" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF35" s="21">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AG35" s="22">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="AH35" s="20">
-        <v>5.18</v>
+        <v>6.85</v>
       </c>
       <c r="AI35" s="16">
         <v>0.91</v>
@@ -12214,11 +12228,11 @@
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>310</v>
+        <v>1901</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
@@ -12232,11 +12246,11 @@
         <v>10</v>
       </c>
       <c r="AR35" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>GOTTSCHALL GALEN LTD</t>
+          <t>Vytronix</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
@@ -12251,20 +12265,16 @@
       </c>
       <c r="AV35" s="14" t="inlineStr">
         <is>
-          <t>United Kingdom E16 2GP GB</t>
+          <t>Dunstable Bedfordshire LU5 5UL GB</t>
         </is>
       </c>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2F8EA95F3IAV8</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
         </is>
       </c>
       <c r="AX35" s="13"/>
-      <c r="AY35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY35" s="13"/>
       <c r="AZ35" s="13"/>
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
@@ -12282,49 +12292,41 @@
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
       <c r="BH35" s="14"/>
-      <c r="BI35" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI35" s="23"/>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>5.18 kg</t>
+          <t>6 Kilograms</t>
         </is>
       </c>
       <c r="BK35" s="23" t="inlineStr">
         <is>
-          <t>5.18 kg</t>
+          <t>6.00 kg</t>
         </is>
       </c>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>39 x 35 x 20 cm</t>
-        </is>
-      </c>
-      <c r="BM35" s="23" t="inlineStr">
-        <is>
-          <t>39.00 x 35.00 x 20.00 cm</t>
-        </is>
-      </c>
+          <t>36.5W centimetres</t>
+        </is>
+      </c>
+      <c r="BM35" s="23"/>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>5.18 kg</t>
+          <t>10.32 kg</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>5.18 kg</t>
+          <t>10.32 kg</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>38.5 x 34.5 x 20.5 cm</t>
+          <t>55.5 x 40 x 38 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>38.50 x 34.50 x 20.50 cm</t>
+          <t>55.50 x 40.00 x 38.00 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
@@ -12340,40 +12342,40 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B096KMBG8K</t>
+          <t>B0GCZXR7BP</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX</t>
+          <t>uwant</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B096KMBG8K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/uwant/b/ref=bl_dp_s_web_91770098031?ie=UTF8&amp;node=91770098031&amp;field-lbr_brands_browse-bin=uwant</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>VYTRONIX WSH60 Multi-Function Wet &amp; Dry Vacuum Cleaner &amp; Carpet CleanersPortable 4-in-1 Carpet Washer and Floor Cleaner wit</t>
+          <t>Uwant Y100 Steam Carpet Cleaner Machine, 1750W 18kPa, 7-in-1 Multi-ToolssSelf-Cleaning Hose, for Multi-Surface Spills/Pet M</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B096KMBG8K?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/415g5BMj1rL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41SUDAA37WL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B096KMBG8K</t>
+          <t>B0GCZXR7BP</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -12387,13 +12389,13 @@
         </is>
       </c>
       <c r="O36" s="15">
-        <v>106836</v>
+        <v>55512</v>
       </c>
       <c r="P36" s="15">
-        <v>-37979</v>
+        <v>36346</v>
       </c>
       <c r="Q36" s="16">
-        <v>-0.55</v>
+        <v>0.4</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
@@ -12402,63 +12404,55 @@
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>52</t>
         </is>
       </c>
       <c r="T36" s="15">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="U36" s="16">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="V36" s="15">
-        <v>11519</v>
-      </c>
-      <c r="W36" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X36" s="15">
-        <v>7999</v>
-      </c>
+        <v>11088</v>
+      </c>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
       <c r="Y36" s="19">
         <v>1</v>
       </c>
       <c r="Z36" s="20">
-        <v>79.99</v>
+        <v>99</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
-      <c r="AC36" s="15">
-        <v>25</v>
-      </c>
+      <c r="AC36" s="15"/>
       <c r="AD36" s="19">
-        <v>1189</v>
+        <v>77</v>
       </c>
       <c r="AE36" s="15">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="AF36" s="21">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AG36" s="22">
-        <v>0.0208</v>
+        <v>0.6339</v>
       </c>
       <c r="AH36" s="20">
-        <v>6.85</v>
+        <v>5.94</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.91</v>
+        <v>0.94</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>1901</v>
+        <v>226</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
@@ -12472,11 +12466,11 @@
         <v>10</v>
       </c>
       <c r="AR36" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>Vytronix</t>
+          <t>SpotZapper</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
@@ -12486,21 +12480,25 @@
       </c>
       <c r="AU36" s="13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV36" s="14" t="inlineStr">
         <is>
-          <t>Dunstable Bedfordshire LU5 5UL GB</t>
+          <t>芜湖市 安徽省 241399 CN</t>
         </is>
       </c>
       <c r="AW36" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17T2O4U8TIBEZ</t>
         </is>
       </c>
       <c r="AX36" s="13"/>
-      <c r="AY36" s="13"/>
+      <c r="AY36" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ36" s="13"/>
       <c r="BA36" s="13"/>
       <c r="BB36" s="13"/>
@@ -12518,41 +12516,49 @@
       <c r="BF36" s="13"/>
       <c r="BG36" s="13"/>
       <c r="BH36" s="14"/>
-      <c r="BI36" s="23"/>
+      <c r="BI36" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>6 Kilograms</t>
+          <t>6.69 kg</t>
         </is>
       </c>
       <c r="BK36" s="23" t="inlineStr">
         <is>
-          <t>6.00 kg</t>
+          <t>6.69 kg</t>
         </is>
       </c>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>36.5W centimetres</t>
-        </is>
-      </c>
-      <c r="BM36" s="23"/>
+          <t>35.6 x 18.3 x 31 cm</t>
+        </is>
+      </c>
+      <c r="BM36" s="23" t="inlineStr">
+        <is>
+          <t>35.60 x 18.30 x 31.00 cm</t>
+        </is>
+      </c>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>10.32 kg</t>
+          <t>6.69 kg</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>10.32 kg</t>
+          <t>6.69 kg</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>55.5 x 40 x 38 cm</t>
+          <t>49 x 38.2 x 28.2 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>55.50 x 40.00 x 38.00 cm</t>
+          <t>49.00 x 38.20 x 28.20 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
@@ -12568,40 +12574,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GCZXR7BP</t>
+          <t>B0DJMCBY4B</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>uwant</t>
+          <t>Vacmaster</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/uwant/b/ref=bl_dp_s_web_91770098031?ie=UTF8&amp;node=91770098031&amp;field-lbr_brands_browse-bin=uwant</t>
+          <t>https://www.amazon.co.uk/stores/Vacmaster/page/75F2E189-B394-439E-9CC9-6F4AB03DFAE5?lp_asin=B0DJMCBY4B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Uwant Y100 Steam Carpet Cleaner Machine, 1750W 18kPa, 7-in-1 Multi-ToolssSelf-Cleaning Hose, for Multi-Surface Spills/Pet M</t>
+          <t>Vacmaster EasyClean Up Compact Carpet Spot Cleaner, CordedsSmall carpet cleaner for carpet, stairs &amp; upholstery. 550W motor</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DJMCBY4B?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41SUDAA37WL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41PLSFp59LL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GCZXR7BP</t>
+          <t>B0DJMCBY4B</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -12615,13 +12621,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>55512</v>
+        <v>29633</v>
       </c>
       <c r="P37" s="15">
-        <v>36346</v>
+        <v>13256</v>
       </c>
       <c r="Q37" s="16">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -12630,59 +12636,59 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="U37" s="16">
-        <v>-0.6</v>
+        <v>0.49</v>
       </c>
       <c r="V37" s="15">
-        <v>11088</v>
+        <v>9838</v>
       </c>
       <c r="W37" s="15"/>
       <c r="X37" s="15"/>
       <c r="Y37" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z37" s="20">
-        <v>99</v>
+        <v>59.99</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="15"/>
       <c r="AD37" s="19">
-        <v>77</v>
+        <v>491</v>
       </c>
       <c r="AE37" s="15">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="AF37" s="21">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AG37" s="22">
-        <v>0.6339</v>
+        <v>0.012199999999999999</v>
       </c>
       <c r="AH37" s="20">
-        <v>5.94</v>
+        <v>5.33</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.94</v>
+        <v>0.91</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>226</v>
+        <v>690</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN37" s="13"/>
@@ -12692,33 +12698,21 @@
         <v>10</v>
       </c>
       <c r="AR37" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>SpotZapper</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU37" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV37" s="14" t="inlineStr">
-        <is>
-          <t>芜湖市 安徽省 241399 CN</t>
-        </is>
-      </c>
-      <c r="AW37" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17T2O4U8TIBEZ</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU37" s="13"/>
+      <c r="AV37" s="14"/>
+      <c r="AW37" s="13"/>
       <c r="AX37" s="13"/>
       <c r="AY37" s="13" t="inlineStr">
         <is>
@@ -12749,42 +12743,38 @@
       </c>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>6.69 kg</t>
+          <t>3.5 Kilograms</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>6.69 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>35.6 x 18.3 x 31 cm</t>
-        </is>
-      </c>
-      <c r="BM37" s="23" t="inlineStr">
-        <is>
-          <t>35.60 x 18.30 x 31.00 cm</t>
-        </is>
-      </c>
+          <t>23D x 34W x 36H centimetres</t>
+        </is>
+      </c>
+      <c r="BM37" s="23"/>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>6.69 kg</t>
+          <t>4.77 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>6.69 kg</t>
+          <t>4.77 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>49 x 38.2 x 28.2 cm</t>
+          <t>37.3 x 34.4 x 23.3 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>49.00 x 38.20 x 28.20 cm</t>
+          <t>37.30 x 34.40 x 23.30 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
@@ -12800,40 +12790,40 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0DJMCBY4B</t>
+          <t>B0GDDKS6ZJ</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster</t>
+          <t>HYCHIKA BETTER TOOLS FOR BETTER LIFE</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Vacmaster/page/75F2E189-B394-439E-9CC9-6F4AB03DFAE5?lp_asin=B0DJMCBY4B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/B7CD0F54-C752-439A-AD08-CA062A6946FF?lp_asin=B0GDDKS6ZJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster EasyClean Up Compact Carpet Spot Cleaner, CordedsSmall carpet cleaner for carpet, stairs &amp; upholstery. 550W motor</t>
+          <t>HYCHIKA Carpet Spot Cleaner 1800W, 17 kPa Portable Upholstery Carpet machine with Separate Tanks &amp; Self-Clean, Handheld carpe</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DJMCBY4B?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GDDKS6ZJ?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41PLSFp59LL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71ppKXUCKdL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0DJMCBY4B</t>
+          <t>B0GDDKS6ZJ</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -12847,13 +12837,13 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>29633</v>
+        <v>27235</v>
       </c>
       <c r="P38" s="15">
-        <v>13256</v>
+        <v>228744</v>
       </c>
       <c r="Q38" s="16">
-        <v>0.31</v>
+        <v>0.89</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -12862,59 +12852,65 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="U38" s="16">
-        <v>0.49</v>
+        <v>0.83</v>
       </c>
       <c r="V38" s="15">
-        <v>9838</v>
-      </c>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
+        <v>9519</v>
+      </c>
+      <c r="W38" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X38" s="15">
+        <v>7755</v>
+      </c>
       <c r="Y38" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z38" s="20">
-        <v>59.99</v>
+        <v>83.32</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="15"/>
       <c r="AD38" s="19">
-        <v>491</v>
+        <v>32</v>
       </c>
       <c r="AE38" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF38" s="21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG38" s="22">
-        <v>0.012199999999999999</v>
+        <v>0.0084</v>
       </c>
       <c r="AH38" s="20">
         <v>5.33</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>690</v>
+        <v>83</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN38" s="13"/>
@@ -12924,27 +12920,35 @@
         <v>10</v>
       </c>
       <c r="AR38" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS38" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>XLN (UK)</t>
         </is>
       </c>
       <c r="AT38" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU38" s="13"/>
-      <c r="AV38" s="14"/>
-      <c r="AW38" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU38" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV38" s="14" t="inlineStr">
+        <is>
+          <t>Longgang Guangdong 518111 CN</t>
+        </is>
+      </c>
+      <c r="AW38" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGEBNOEX5B7LS</t>
+        </is>
+      </c>
       <c r="AX38" s="13"/>
-      <c r="AY38" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY38" s="13"/>
       <c r="AZ38" s="13"/>
       <c r="BA38" s="13"/>
       <c r="BB38" s="13"/>
@@ -12962,45 +12966,45 @@
       <c r="BF38" s="13"/>
       <c r="BG38" s="13"/>
       <c r="BH38" s="14"/>
-      <c r="BI38" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI38" s="23"/>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>3.5 Kilograms</t>
+          <t>5.5 kg</t>
         </is>
       </c>
       <c r="BK38" s="23" t="inlineStr">
         <is>
-          <t>3.50 kg</t>
+          <t>5.50 kg</t>
         </is>
       </c>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>23D x 34W x 36H centimetres</t>
-        </is>
-      </c>
-      <c r="BM38" s="23"/>
+          <t>19 x 43 x 33 cm</t>
+        </is>
+      </c>
+      <c r="BM38" s="23" t="inlineStr">
+        <is>
+          <t>19.00 x 43.00 x 33.00 cm</t>
+        </is>
+      </c>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>4.77 kg</t>
+          <t>5.53 kg</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>4.77 kg</t>
+          <t>5.53 kg</t>
         </is>
       </c>
       <c r="BP38" s="23" t="inlineStr">
         <is>
-          <t>37.3 x 34.4 x 23.3 cm</t>
+          <t>43.8 x 34.6 x 20.2 cm</t>
         </is>
       </c>
       <c r="BQ38" s="23" t="inlineStr">
         <is>
-          <t>37.30 x 34.40 x 23.30 cm</t>
+          <t>43.80 x 34.60 x 20.20 cm</t>
         </is>
       </c>
       <c r="BR38" s="13" t="inlineStr">
@@ -13016,40 +13020,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GDDKS6ZJ</t>
+          <t>B0DMTFH97X</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>HYCHIKA BETTER TOOLS FOR BETTER LIFE</t>
+          <t>Abode</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/B7CD0F54-C752-439A-AD08-CA062A6946FF?lp_asin=B0GDDKS6ZJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/Abode/b/ref=bl_dp_s_web_61386520031?ie=UTF8&amp;node=61386520031&amp;field-lbr_brands_browse-bin=Abode</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>HYCHIKA Carpet Spot Cleaner 1800W, 17 kPa Portable Upholstery Carpet machine with Separate Tanks &amp; Self-Clean, Handheld carpe</t>
+          <t>Abode Compact &amp; Lightweight Spot Cleaner Carpet Washer 800ml Water Tank Stain Remover, Cleans Spills from Carpets, Stairs, Up</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GDDKS6ZJ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DMTFH97X?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71ppKXUCKdL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71d09y-wiwL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GDDKS6ZJ</t>
+          <t>B0DMTFH97X</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -13063,13 +13067,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>27235</v>
+        <v>13181</v>
       </c>
       <c r="P39" s="15">
-        <v>228744</v>
+        <v>3985</v>
       </c>
       <c r="Q39" s="16">
-        <v>0.89</v>
+        <v>0.23</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -13078,17 +13082,17 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>22</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>119</v>
+        <v>192</v>
       </c>
       <c r="U39" s="16">
-        <v>0.83</v>
+        <v>0.45</v>
       </c>
       <c r="V39" s="15">
-        <v>9519</v>
+        <v>8638</v>
       </c>
       <c r="W39" s="15" t="inlineStr">
         <is>
@@ -13096,93 +13100,93 @@
         </is>
       </c>
       <c r="X39" s="15">
-        <v>7755</v>
+        <v>4021</v>
       </c>
       <c r="Y39" s="19">
         <v>1</v>
       </c>
       <c r="Z39" s="20">
-        <v>83.32</v>
+        <v>41.66</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="15"/>
       <c r="AD39" s="19">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AE39" s="15">
         <v>1</v>
       </c>
       <c r="AF39" s="21">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AG39" s="22">
-        <v>0.0084</v>
+        <v>0.0052</v>
       </c>
       <c r="AH39" s="20">
-        <v>5.33</v>
+        <v>3.43</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>83</v>
+        <v>626</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN39" s="13"/>
       <c r="AO39" s="13"/>
       <c r="AP39"/>
       <c r="AQ39" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR39" s="19">
         <v>2</v>
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>XLN (UK)</t>
+          <t>Electrical Shop</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU39" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV39" s="14" t="inlineStr">
         <is>
-          <t>Longgang Guangdong 518111 CN</t>
+          <t>WIGAN GREATER MANCHESTER WN24AY GB</t>
         </is>
       </c>
       <c r="AW39" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGEBNOEX5B7LS</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A34BWCJVHPX7M7</t>
         </is>
       </c>
       <c r="AX39" s="13"/>
-      <c r="AY39" s="13"/>
+      <c r="AY39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ39" s="13"/>
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
-      <c r="BC39" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC39" s="13"/>
       <c r="BD39" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13192,50 +13196,54 @@
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
       <c r="BH39" s="14"/>
-      <c r="BI39" s="23"/>
+      <c r="BI39" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>5.5 kg</t>
+          <t>3 kg</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>5.50 kg</t>
+          <t>3.00 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>19 x 43 x 33 cm</t>
+          <t>33.6 x 21.5 x 39.1 cm</t>
         </is>
       </c>
       <c r="BM39" s="23" t="inlineStr">
         <is>
-          <t>19.00 x 43.00 x 33.00 cm</t>
+          <t>33.60 x 21.50 x 39.10 cm</t>
         </is>
       </c>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>5.53 kg</t>
+          <t>3.3 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>5.53 kg</t>
+          <t>3.30 kg</t>
         </is>
       </c>
       <c r="BP39" s="23" t="inlineStr">
         <is>
-          <t>43.8 x 34.6 x 20.2 cm</t>
+          <t>35.3 x 32.5 x 20 cm</t>
         </is>
       </c>
       <c r="BQ39" s="23" t="inlineStr">
         <is>
-          <t>43.80 x 34.60 x 20.20 cm</t>
+          <t>35.30 x 32.50 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR39" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -13246,45 +13254,45 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0F2J9921T</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>BISSELL</t>
+          <t>Beldray</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Oxygen Boost Formula Booster for SpotClean 1L 1134NsA cleaning solution booster for use on carpet, upholstery, area</t>
+          <t>Beldray Compact Spotbuster Spot Cleaner With Spray, Scrub, Vacuum, 1.3LsExtendable Hose, Scrubbing Brush Head, Dual Tank 80</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0753NXDPR?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F2J9921T?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31LC0CHQzZL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71l-bqPqPSL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0F2J9921T</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>Pet Supplies:Dogs:Litter &amp; Housetraining:Odour &amp; Stain Removers:Stain Removers</t>
+          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Carpet Washers</t>
         </is>
       </c>
       <c r="N40" s="14" t="inlineStr">
@@ -13293,13 +13301,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>2085</v>
+        <v>28933</v>
       </c>
       <c r="P40" s="15">
-        <v>-165</v>
+        <v>15067</v>
       </c>
       <c r="Q40" s="16">
-        <v>-0.09</v>
+        <v>0.34</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -13308,67 +13316,65 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>956</v>
+        <v>168</v>
       </c>
       <c r="U40" s="16">
-        <v>0.32</v>
+        <v>-0.35</v>
       </c>
       <c r="V40" s="15">
-        <v>9369</v>
+        <v>8398</v>
       </c>
       <c r="W40" s="15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X40" s="15">
-        <v>1960</v>
+        <v>4999</v>
       </c>
       <c r="Y40" s="19">
         <v>4</v>
       </c>
       <c r="Z40" s="20">
-        <v>9.8</v>
+        <v>49.99</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
-      <c r="AC40" s="15">
-        <v>14</v>
-      </c>
+      <c r="AC40" s="15"/>
       <c r="AD40" s="19">
-        <v>9328</v>
+        <v>12</v>
       </c>
       <c r="AE40" s="15">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="AF40" s="21">
         <v>4.6</v>
       </c>
       <c r="AG40" s="22">
-        <v>0.0681</v>
+        <v>0.0179</v>
       </c>
       <c r="AH40" s="20">
-        <v>3.1</v>
+        <v>5.18</v>
       </c>
       <c r="AI40" s="16">
-        <v>0.69</v>
+        <v>0.9</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2019-12-19</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>2446</v>
+        <v>504</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN40" s="13"/>
@@ -13378,16 +13384,16 @@
         <v>10</v>
       </c>
       <c r="AR40" s="19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>Reliapart</t>
+          <t>homeofbrands</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU40" s="13" t="inlineStr">
@@ -13397,12 +13403,12 @@
       </c>
       <c r="AV40" s="14" t="inlineStr">
         <is>
-          <t>Cardiff Cardiff CF3 2PY GB</t>
+          <t>Chadderton Oldham OL9 0DD GB</t>
         </is>
       </c>
       <c r="AW40" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKGAA3WULFPOP</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W</t>
         </is>
       </c>
       <c r="AX40" s="13"/>
@@ -13435,47 +13441,47 @@
       </c>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>7 x 12 x 23.8 cm</t>
+          <t>26 x 22 x 27 cm</t>
         </is>
       </c>
       <c r="BM40" s="23" t="inlineStr">
         <is>
-          <t>7.00 x 12.00 x 23.80 cm</t>
+          <t>26.00 x 22.00 x 27.00 cm</t>
         </is>
       </c>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>3.56 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>3.56 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>23.5 x 11.9 x 6.9 cm</t>
+          <t>36.3 x 35 x 21.6 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>23.50 x 11.90 x 6.90 cm</t>
+          <t>36.30 x 35.00 x 21.60 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -13486,40 +13492,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0DMTFH97X</t>
+          <t>B0CZRYCLNT</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Abode</t>
+          <t>Daewoo</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/Abode/b/ref=bl_dp_s_web_61386520031?ie=UTF8&amp;node=61386520031&amp;field-lbr_brands_browse-bin=Abode</t>
+          <t>https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Abode Compact &amp; Lightweight Spot Cleaner Carpet Washer 800ml Water Tank Stain Remover, Cleans Spills from Carpets, Stairs, Up</t>
+          <t>Daewoo Stairmaster Corded Spotwasher</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DMTFH97X?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71d09y-wiwL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0DMTFH97X</t>
+          <t>B0CZRYCLNT</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -13533,13 +13539,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>13181</v>
+        <v>34091</v>
       </c>
       <c r="P41" s="15">
-        <v>3985</v>
+        <v>-2151</v>
       </c>
       <c r="Q41" s="16">
-        <v>0.23</v>
+        <v>-0.07</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -13548,49 +13554,49 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="U41" s="16">
-        <v>0.45</v>
+        <v>-0.09</v>
       </c>
       <c r="V41" s="15">
-        <v>8638</v>
+        <v>6798</v>
       </c>
       <c r="W41" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X41" s="15">
-        <v>4021</v>
+        <v>2279</v>
       </c>
       <c r="Y41" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z41" s="20">
-        <v>41.66</v>
+        <v>35.41</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="15"/>
       <c r="AD41" s="19">
-        <v>50</v>
+        <v>315</v>
       </c>
       <c r="AE41" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF41" s="21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.0052</v>
+        <v>0.025</v>
       </c>
       <c r="AH41" s="20">
-        <v>3.43</v>
+        <v>3.61</v>
       </c>
       <c r="AI41" s="16">
         <v>0.92</v>
@@ -13598,51 +13604,39 @@
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>626</v>
+        <v>878</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
       <c r="AO41" s="13"/>
       <c r="AP41"/>
       <c r="AQ41" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR41" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>Electrical Shop</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU41" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV41" s="14" t="inlineStr">
-        <is>
-          <t>WIGAN GREATER MANCHESTER WN24AY GB</t>
-        </is>
-      </c>
-      <c r="AW41" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A34BWCJVHPX7M7</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU41" s="13"/>
+      <c r="AV41" s="14"/>
+      <c r="AW41" s="13"/>
       <c r="AX41" s="13"/>
       <c r="AY41" s="13" t="inlineStr">
         <is>
@@ -13669,42 +13663,42 @@
       </c>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>3 kg</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>3.00 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>33.6 x 21.5 x 39.1 cm</t>
+          <t>35 x 20 x 23 cm</t>
         </is>
       </c>
       <c r="BM41" s="23" t="inlineStr">
         <is>
-          <t>33.60 x 21.50 x 39.10 cm</t>
+          <t>35.00 x 20.00 x 23.00 cm</t>
         </is>
       </c>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>3.3 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>3.30 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>35.3 x 32.5 x 20 cm</t>
+          <t>41.5 x 25.5 x 20.1 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>35.30 x 32.50 x 20.00 cm</t>
+          <t>41.50 x 25.50 x 20.10 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
@@ -13720,40 +13714,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0F2J9921T</t>
+          <t>B0FZBSDZ26</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Beldray</t>
+          <t>VonHaus</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0FZBSDZ26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Beldray Compact Spotbuster Spot Cleaner With Spray, Scrub, Vacuum, 1.3LsExtendable Hose, Scrubbing Brush Head, Dual Tank 80</t>
+          <t>Vonhaus Spot Cleaner 600W Handheld Carpet Cleaner with Crevice &amp; Pet Brushs1.5L Carpet Washer &amp; Sofa Cleaner Machine with S</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F2J9921T?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71l-bqPqPSL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71Dl6k2D2FL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0F2J9921T</t>
+          <t>B0FZBSDZ26</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -13767,13 +13761,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>28933</v>
+        <v>32738</v>
       </c>
       <c r="P42" s="15">
-        <v>15067</v>
+        <v>86422</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.34</v>
+        <v>0.73</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -13782,37 +13776,37 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="U42" s="16">
-        <v>-0.35</v>
+        <v>-0.4</v>
       </c>
       <c r="V42" s="15">
-        <v>8398</v>
+        <v>6659</v>
       </c>
       <c r="W42" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X42" s="15">
-        <v>4999</v>
+        <v>3101</v>
       </c>
       <c r="Y42" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="20">
-        <v>49.99</v>
+        <v>59.99</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="15"/>
       <c r="AD42" s="19">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="AE42" s="15">
         <v>3</v>
@@ -13821,22 +13815,22 @@
         <v>4.6</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.0179</v>
+        <v>0.027000000000000003</v>
       </c>
       <c r="AH42" s="20">
         <v>5.18</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>504</v>
+        <v>300</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
@@ -13854,7 +13848,7 @@
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>homeofbrands</t>
+          <t>VonHaus UK</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
@@ -13869,12 +13863,12 @@
       </c>
       <c r="AV42" s="14" t="inlineStr">
         <is>
-          <t>Chadderton Oldham OL9 0DD GB</t>
+          <t>SALFORD Manchester M3 7BF GB</t>
         </is>
       </c>
       <c r="AW42" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6</t>
         </is>
       </c>
       <c r="AX42" s="13"/>
@@ -13907,42 +13901,42 @@
       </c>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>26 x 22 x 27 cm</t>
+          <t>17.3 x 30.6 x 32.6 cm</t>
         </is>
       </c>
       <c r="BM42" s="23" t="inlineStr">
         <is>
-          <t>26.00 x 22.00 x 27.00 cm</t>
+          <t>17.30 x 30.60 x 32.60 cm</t>
         </is>
       </c>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>3.56 kg</t>
+          <t>4.8 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>3.56 kg</t>
+          <t>4.80 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>36.3 x 35 x 21.6 cm</t>
+          <t>40 x 35 x 20 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>36.30 x 35.00 x 21.60 cm</t>
+          <t>40.00 x 35.00 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
@@ -13958,40 +13952,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0CZRYCLNT</t>
+          <t>B09JSVWX57</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>Daewoo</t>
+          <t>Tower</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09JSVWX57&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Daewoo Stairmaster Corded Spotwasher</t>
+          <t>Tower T548005 AquajetPlus Spot Cleaner with Suction Nozzle &amp; Brush, 1.2L Clean &amp; Dirty Water Tanks, 1.2m Hose, 400W, Grey &amp; B</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09JSVWX57?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41uf-z8AXOL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0CZRYCLNT</t>
+          <t>B09JSVWX57</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -14001,36 +13995,38 @@
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="O43" s="15">
-        <v>34091</v>
+        <v>19834</v>
       </c>
       <c r="P43" s="15">
-        <v>-2151</v>
+        <v>10363</v>
       </c>
       <c r="Q43" s="16">
-        <v>-0.07</v>
+        <v>0.34</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
-          <t>Carpet Washers</t>
+          <t>Carpet Washers
+Home Care &amp; Cleaning</t>
         </is>
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>56
+8293</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="U43" s="16">
-        <v>-0.09</v>
+        <v>1.88</v>
       </c>
       <c r="V43" s="15">
-        <v>6798</v>
+        <v>6239</v>
       </c>
       <c r="W43" s="15" t="inlineStr">
         <is>
@@ -14038,43 +14034,43 @@
         </is>
       </c>
       <c r="X43" s="15">
-        <v>2279</v>
+        <v>3278</v>
       </c>
       <c r="Y43" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z43" s="20">
-        <v>35.41</v>
+        <v>49.99</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="15"/>
       <c r="AD43" s="19">
-        <v>315</v>
+        <v>473</v>
       </c>
       <c r="AE43" s="15">
         <v>4</v>
       </c>
       <c r="AF43" s="21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.025</v>
+        <v>0.0385</v>
       </c>
       <c r="AH43" s="20">
-        <v>3.61</v>
+        <v>3.43</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>878</v>
+        <v>1775</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
@@ -14085,10 +14081,10 @@
       <c r="AO43" s="13"/>
       <c r="AP43"/>
       <c r="AQ43" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR43" s="19">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
@@ -14112,7 +14108,11 @@
       <c r="AZ43" s="13"/>
       <c r="BA43" s="13"/>
       <c r="BB43" s="13"/>
-      <c r="BC43" s="13"/>
+      <c r="BC43" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD43" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -14129,42 +14129,38 @@
       </c>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>3.5 Kilograms</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>35 x 20 x 23 cm</t>
-        </is>
-      </c>
-      <c r="BM43" s="23" t="inlineStr">
-        <is>
-          <t>35.00 x 20.00 x 23.00 cm</t>
-        </is>
-      </c>
+          <t>19L x 27W x 29H centimetres</t>
+        </is>
+      </c>
+      <c r="BM43" s="23"/>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>3.99 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>3.99 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>41.5 x 25.5 x 20.1 cm</t>
+          <t>35.7 x 32.6 x 20 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>41.50 x 25.50 x 20.10 cm</t>
+          <t>35.70 x 32.60 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
@@ -14180,40 +14176,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0FZBSDZ26</t>
+          <t>B0B4JST7J8</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>VonHaus</t>
+          <t>Swan</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0FZBSDZ26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Vonhaus Spot Cleaner 600W Handheld Carpet Cleaner with Crevice &amp; Pet Brushs1.5L Carpet Washer &amp; Sofa Cleaner Machine with S</t>
+          <t>Swan TV’s Queen of Clean Handheld Carpet Cleaner with 5m Power Cord, 480ml Water Tank, 500W, Pink, SC18410QOCN</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71Dl6k2D2FL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0FZBSDZ26</t>
+          <t>B0B4JST7J8</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -14227,13 +14223,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>32738</v>
+        <v>38790</v>
       </c>
       <c r="P44" s="15">
-        <v>86422</v>
+        <v>65636</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -14242,17 +14238,17 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="U44" s="16">
-        <v>-0.4</v>
+        <v>0.19</v>
       </c>
       <c r="V44" s="15">
-        <v>6659</v>
+        <v>4639</v>
       </c>
       <c r="W44" s="15" t="inlineStr">
         <is>
@@ -14260,31 +14256,31 @@
         </is>
       </c>
       <c r="X44" s="15">
-        <v>3101</v>
+        <v>2233</v>
       </c>
       <c r="Y44" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z44" s="20">
-        <v>59.99</v>
+        <v>33.32</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="15"/>
       <c r="AD44" s="19">
-        <v>59</v>
+        <v>507</v>
       </c>
       <c r="AE44" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF44" s="21">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AG44" s="22">
-        <v>0.027000000000000003</v>
+        <v>0</v>
       </c>
       <c r="AH44" s="20">
-        <v>5.18</v>
+        <v>3.43</v>
       </c>
       <c r="AI44" s="16">
         <v>0.91</v>
@@ -14292,15 +14288,15 @@
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>300</v>
+        <v>1529</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN44" s="13"/>
@@ -14310,39 +14306,23 @@
         <v>10</v>
       </c>
       <c r="AR44" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>VonHaus UK</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU44" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV44" s="14" t="inlineStr">
-        <is>
-          <t>SALFORD Manchester M3 7BF GB</t>
-        </is>
-      </c>
-      <c r="AW44" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU44" s="13"/>
+      <c r="AV44" s="14"/>
+      <c r="AW44" s="13"/>
       <c r="AX44" s="13"/>
-      <c r="AY44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY44" s="13"/>
       <c r="AZ44" s="13"/>
       <c r="BA44" s="13"/>
       <c r="BB44" s="13"/>
@@ -14360,54 +14340,50 @@
       <c r="BF44" s="13"/>
       <c r="BG44" s="13"/>
       <c r="BH44" s="14"/>
-      <c r="BI44" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI44" s="23"/>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>4 kg</t>
+          <t>2.58 kg</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>2.58 kg</t>
         </is>
       </c>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>17.3 x 30.6 x 32.6 cm</t>
+          <t>23 x 20 x 34 cm</t>
         </is>
       </c>
       <c r="BM44" s="23" t="inlineStr">
         <is>
-          <t>17.30 x 30.60 x 32.60 cm</t>
+          <t>23.00 x 20.00 x 34.00 cm</t>
         </is>
       </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>4.8 kg</t>
+          <t>3.29 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>4.80 kg</t>
+          <t>3.29 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>40 x 35 x 20 cm</t>
+          <t>41.1 x 24.6 x 20.6 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>40.00 x 35.00 x 20.00 cm</t>
+          <t>41.10 x 24.60 x 20.60 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -14418,40 +14394,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B09JSVWX57</t>
+          <t>B0H6KDXVQ5</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Tower</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09JSVWX57&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0H6KDXVQ5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Tower T548005 AquajetPlus Spot Cleaner with Suction Nozzle &amp; Brush, 1.2L Clean &amp; Dirty Water Tanks, 1.2m Hose, 400W, Grey &amp; B</t>
+          <t>Shark CarpetForce Ultra Upright Carpet Cleaner with HairPro, EX550UKCPs2 Bottles of Deep Clean Ultra Solution, PowerFins Br</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09JSVWX57?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H6KDXVQ5?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41uf-z8AXOL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31R6lJG42+L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B09JSVWX57</t>
+          <t>B0H6KDXVQ5</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -14461,82 +14437,72 @@
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="O45" s="15">
-        <v>19834</v>
+        <v>56238</v>
       </c>
       <c r="P45" s="15">
-        <v>10363</v>
+        <v>-162646</v>
       </c>
       <c r="Q45" s="16">
-        <v>0.34</v>
+        <v>-0.37</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
-          <t>Carpet Washers
-Home Care &amp; Cleaning</t>
+          <t>Carpet Washers</t>
         </is>
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>56
-8293</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>104</v>
-      </c>
-      <c r="U45" s="16">
-        <v>1.88</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="U45" s="16"/>
       <c r="V45" s="15">
-        <v>6239</v>
-      </c>
-      <c r="W45" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X45" s="15">
-        <v>3278</v>
-      </c>
+        <v>3870</v>
+      </c>
+      <c r="W45" s="15"/>
+      <c r="X45" s="15"/>
       <c r="Y45" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>49.99</v>
+        <v>179.16</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="15"/>
       <c r="AD45" s="19">
-        <v>473</v>
+        <v>28</v>
       </c>
       <c r="AE45" s="15">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.0385</v>
+        <v>0.8332999999999999</v>
       </c>
       <c r="AH45" s="20">
-        <v>3.43</v>
+        <v>7</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.94</v>
+        <v>0.97</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>1775</v>
+        <v>66</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
@@ -14550,7 +14516,7 @@
         <v>10</v>
       </c>
       <c r="AR45" s="19">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
@@ -14595,43 +14561,43 @@
       </c>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>3.5 Kilograms</t>
+          <t>15.21 Pounds</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>3.50 kg</t>
+          <t>6.90 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>19L x 27W x 29H centimetres</t>
+          <t>32.7D x 26.4W x 110.9H centimetres</t>
         </is>
       </c>
       <c r="BM45" s="23"/>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>3.99 kg</t>
+          <t>10.21 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>3.99 kg</t>
+          <t>10.21 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>35.7 x 32.6 x 20 cm</t>
+          <t>71.8 x 38.8 x 31.2 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>35.70 x 32.60 x 20.00 cm</t>
+          <t>71.80 x 38.80 x 31.20 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -14642,40 +14608,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0B4JST7J8</t>
+          <t>B08GSPYJ68</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Swan</t>
+          <t>Ewbank</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Ewbank/page/379635B0-DB01-48B5-9749-216DB75EB5AC?lp_asin=B08GSPYJ68&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Swan TV’s Queen of Clean Handheld Carpet Cleaner with 5m Power Cord, 480ml Water Tank, 500W, Pink, SC18410QOCN</t>
+          <t>Ewbank EW0250 Manual Carpet Shampooer, Twin Nylon Brush Strips, Polymer Fibre Roller, Lightweight Upright Carpet &amp; Upholstery</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B08GSPYJ68?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/41CrruJ27DL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0B4JST7J8</t>
+          <t>B08GSPYJ68</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -14689,13 +14655,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>38790</v>
+        <v>38403</v>
       </c>
       <c r="P46" s="15">
-        <v>65636</v>
+        <v>1153</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.63</v>
+        <v>0.03</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -14704,104 +14670,110 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="U46" s="16">
-        <v>0.19</v>
+        <v>-0.36</v>
       </c>
       <c r="V46" s="15">
-        <v>4639</v>
+        <v>3752</v>
       </c>
       <c r="W46" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X46" s="15">
-        <v>2233</v>
+        <v>2699</v>
       </c>
       <c r="Y46" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>33.32</v>
+        <v>26.99</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
-      <c r="AC46" s="15"/>
+      <c r="AC46" s="15">
+        <v>6</v>
+      </c>
       <c r="AD46" s="19">
-        <v>507</v>
+        <v>789</v>
       </c>
       <c r="AE46" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF46" s="21">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AG46" s="22">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="AH46" s="20">
-        <v>3.43</v>
+        <v>5.02</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.91</v>
+        <v>0.81</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>1529</v>
+        <v>2190</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
       <c r="AQ46" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR46" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Go Shop Direct</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
-      <c r="AW46" s="13"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU46" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV46" s="14" t="inlineStr">
+        <is>
+          <t>Bristol BS8 2NT GB</t>
+        </is>
+      </c>
+      <c r="AW46" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29F1JIJWJQSEI</t>
+        </is>
+      </c>
       <c r="AX46" s="13"/>
       <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
-      <c r="BC46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC46" s="13"/>
+      <c r="BD46" s="13"/>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
@@ -14809,47 +14781,47 @@
       <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>2.58 kg</t>
+          <t>1.9 kg</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>2.58 kg</t>
+          <t>1.90 kg</t>
         </is>
       </c>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>23 x 20 x 34 cm</t>
+          <t>90 x 24 x 12 cm</t>
         </is>
       </c>
       <c r="BM46" s="23" t="inlineStr">
         <is>
-          <t>23.00 x 20.00 x 34.00 cm</t>
+          <t>90.00 x 24.00 x 12.00 cm</t>
         </is>
       </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>3.29 kg</t>
+          <t>1.9 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>3.29 kg</t>
+          <t>1.90 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>41.1 x 24.6 x 20.6 cm</t>
+          <t>73 x 26 x 12 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>41.10 x 24.60 x 20.60 cm</t>
+          <t>73.00 x 26.00 x 12.00 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -14860,40 +14832,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0H6KDXVQ5</t>
+          <t>B0FKGYK25M</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>VickyHome</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0H6KDXVQ5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=VickyHome</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Shark CarpetForce Ultra Upright Carpet Cleaner with HairPro, EX550UKCPs2 Bottles of Deep Clean Ultra Solution, PowerFins Br</t>
+          <t>VickyHome Spot Cleaner, 450W Portable Carpet &amp; Upholstery Cleaner Sofa and Carpet Cleaning Machine, Lightweight Handheld Floo</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H6KDXVQ5?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31R6lJG42+L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41G0usLZmPL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0H6KDXVQ5</t>
+          <t>B0FKGYK25M</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -14907,13 +14879,13 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>56238</v>
+        <v>112022</v>
       </c>
       <c r="P47" s="15">
-        <v>-162646</v>
+        <v>31876</v>
       </c>
       <c r="Q47" s="16">
-        <v>-0.37</v>
+        <v>0.4</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -14922,81 +14894,99 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>54</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>18</v>
-      </c>
-      <c r="U47" s="16"/>
+        <v>85</v>
+      </c>
+      <c r="U47" s="16">
+        <v>-0.42</v>
+      </c>
       <c r="V47" s="15">
-        <v>3870</v>
-      </c>
-      <c r="W47" s="15"/>
-      <c r="X47" s="15"/>
+        <v>3023</v>
+      </c>
+      <c r="W47" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X47" s="15">
+        <v>2168</v>
+      </c>
       <c r="Y47" s="19">
         <v>1</v>
       </c>
       <c r="Z47" s="20">
-        <v>179.16</v>
+        <v>35.57</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="15"/>
       <c r="AD47" s="19">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE47" s="15">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AF47" s="21">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AG47" s="22">
-        <v>0.8332999999999999</v>
-      </c>
-      <c r="AH47" s="20">
-        <v>7</v>
-      </c>
+        <v>0.0471</v>
+      </c>
+      <c r="AH47" s="20"/>
       <c r="AI47" s="16">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>66</v>
+        <v>394</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
       <c r="AQ47" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR47" s="19">
         <v>1</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Lucn</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU47" s="13"/>
-      <c r="AV47" s="14"/>
-      <c r="AW47" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU47" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV47" s="14" t="inlineStr">
+        <is>
+          <t>Zengchengqu Guangdongsheng 511300 CN</t>
+        </is>
+      </c>
+      <c r="AW47" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJD9ONY8MI53U</t>
+        </is>
+      </c>
       <c r="AX47" s="13"/>
       <c r="AY47" s="13" t="inlineStr">
         <is>
@@ -15006,16 +14996,8 @@
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
-      <c r="BC47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC47" s="13"/>
+      <c r="BD47" s="13"/>
       <c r="BE47" s="13"/>
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
@@ -15025,47 +15007,15 @@
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ47" s="23" t="inlineStr">
-        <is>
-          <t>15.21 Pounds</t>
-        </is>
-      </c>
-      <c r="BK47" s="23" t="inlineStr">
-        <is>
-          <t>6.90 kg</t>
-        </is>
-      </c>
-      <c r="BL47" s="23" t="inlineStr">
-        <is>
-          <t>32.7D x 26.4W x 110.9H centimetres</t>
-        </is>
-      </c>
+      <c r="BJ47" s="23"/>
+      <c r="BK47" s="23"/>
+      <c r="BL47" s="23"/>
       <c r="BM47" s="23"/>
-      <c r="BN47" s="23" t="inlineStr">
-        <is>
-          <t>10.21 kg</t>
-        </is>
-      </c>
-      <c r="BO47" s="23" t="inlineStr">
-        <is>
-          <t>10.21 kg</t>
-        </is>
-      </c>
-      <c r="BP47" s="23" t="inlineStr">
-        <is>
-          <t>71.8 x 38.8 x 31.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ47" s="23" t="inlineStr">
-        <is>
-          <t>71.80 x 38.80 x 31.20 cm</t>
-        </is>
-      </c>
-      <c r="BR47" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
+      <c r="BN47" s="23"/>
+      <c r="BO47" s="23"/>
+      <c r="BP47" s="23"/>
+      <c r="BQ47" s="23"/>
+      <c r="BR47" s="13"/>
     </row>
     <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
@@ -15074,40 +15024,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B08GSPYJ68</t>
+          <t>B01LX6WOFS</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Ewbank</t>
+          <t>Ecozone</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Ewbank/page/379635B0-DB01-48B5-9749-216DB75EB5AC?lp_asin=B08GSPYJ68&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Ewbank EW0250 Manual Carpet Shampooer, Twin Nylon Brush Strips, Polymer Fibre Roller, Lightweight Upright Carpet &amp; Upholstery</t>
+          <t>EcoZone Carpet Shampoo Solution, Deep Cleans Upholstery, Manual &amp; Machine Cleaning, Fresh Cotton Scent, 3-in-1 Plant Based St</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B08GSPYJ68?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/41CrruJ27DL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B08GSPYJ68</t>
+          <t>B01LX6WOFS</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -15121,13 +15071,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>38403</v>
+        <v>22492</v>
       </c>
       <c r="P48" s="15">
-        <v>1153</v>
+        <v>5850</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.03</v>
+        <v>0.21</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -15136,17 +15086,17 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="U48" s="16">
-        <v>-0.36</v>
+        <v>-0.23</v>
       </c>
       <c r="V48" s="15">
-        <v>3752</v>
+        <v>1678</v>
       </c>
       <c r="W48" s="15" t="inlineStr">
         <is>
@@ -15154,140 +15104,144 @@
         </is>
       </c>
       <c r="X48" s="15">
-        <v>2699</v>
+        <v>762</v>
       </c>
       <c r="Y48" s="19">
         <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>26.99</v>
+        <v>7.66</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AD48" s="19">
-        <v>789</v>
+        <v>902</v>
       </c>
       <c r="AE48" s="15">
         <v>1</v>
       </c>
       <c r="AF48" s="21">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.0072</v>
+        <v>0.0046</v>
       </c>
       <c r="AH48" s="20">
-        <v>5.02</v>
+        <v>3.1</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.81</v>
+        <v>0.6</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2017-05-30</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>2190</v>
+        <v>3379</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48"/>
       <c r="AQ48" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AR48" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Go Shop Direct</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU48" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV48" s="14" t="inlineStr">
-        <is>
-          <t>Bristol BS8 2NT GB</t>
-        </is>
-      </c>
-      <c r="AW48" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29F1JIJWJQSEI</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU48" s="13"/>
+      <c r="AV48" s="14"/>
+      <c r="AW48" s="13"/>
       <c r="AX48" s="13"/>
-      <c r="AY48" s="13"/>
+      <c r="AY48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
-      <c r="BC48" s="13"/>
-      <c r="BD48" s="13"/>
+      <c r="BC48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE48" s="13"/>
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
-      <c r="BI48" s="23"/>
+      <c r="BI48" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>1.9 kg</t>
+          <t>0.43 g</t>
         </is>
       </c>
       <c r="BK48" s="23" t="inlineStr">
         <is>
-          <t>1.90 kg</t>
+          <t>0.43 g</t>
         </is>
       </c>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>90 x 24 x 12 cm</t>
+          <t>8 x 12 x 25 cm</t>
         </is>
       </c>
       <c r="BM48" s="23" t="inlineStr">
         <is>
-          <t>90.00 x 24.00 x 12.00 cm</t>
+          <t>8.00 x 12.00 x 25.00 cm</t>
         </is>
       </c>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>1.9 kg</t>
+          <t>1.06 kg</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>1.90 kg</t>
+          <t>1.06 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>73 x 26 x 12 cm</t>
+          <t>23.4 x 11.9 x 7 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>73.00 x 26.00 x 12.00 cm</t>
+          <t>23.40 x 11.90 x 7.00 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -15298,167 +15252,85 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0FKGYK25M</t>
+          <t>B0CFV7HZHH</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>VickyHome</t>
-        </is>
-      </c>
+      <c r="F49" s="14"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=VickyHome</t>
+          <t>https://www.amazon.co.ukundefined</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>VickyHome Spot Cleaner, 450W Portable Carpet &amp; Upholstery Cleaner Sofa and Carpet Cleaning Machine, Lightweight Handheld Floo</t>
+          <t>Shark StainStriker Stain and Spot Cleaner, Blue PX200UK, 2 Tools, PX200UKsCompact Carpet and Upholstery Cleaner with Powerf</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CFV7HZHH?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41G0usLZmPL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/719JsBbXXGL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0FKGYK25M</t>
-        </is>
-      </c>
-      <c r="M49" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Carpet Washers</t>
-        </is>
-      </c>
-      <c r="N49" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O49" s="15">
-        <v>112022</v>
-      </c>
-      <c r="P49" s="15">
-        <v>31876</v>
-      </c>
-      <c r="Q49" s="16">
-        <v>0.4</v>
-      </c>
-      <c r="R49" s="17" t="inlineStr">
-        <is>
-          <t>Carpet Washers</t>
-        </is>
-      </c>
-      <c r="S49" s="18" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="T49" s="15">
-        <v>85</v>
-      </c>
-      <c r="U49" s="16">
-        <v>-0.42</v>
-      </c>
-      <c r="V49" s="15">
-        <v>3023</v>
-      </c>
-      <c r="W49" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X49" s="15">
-        <v>2168</v>
-      </c>
-      <c r="Y49" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="20">
-        <v>35.57</v>
-      </c>
+          <t>B0CFV7HZHH</t>
+        </is>
+      </c>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="15"/>
+      <c r="U49" s="16"/>
+      <c r="V49" s="15"/>
+      <c r="W49" s="15"/>
+      <c r="X49" s="15"/>
+      <c r="Y49" s="19"/>
+      <c r="Z49" s="20"/>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="19">
-        <v>23</v>
-      </c>
-      <c r="AE49" s="15">
-        <v>4</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="AE49" s="15"/>
       <c r="AF49" s="21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.0471</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="20"/>
       <c r="AI49" s="16">
         <v>0</v>
       </c>
       <c r="AJ49"/>
-      <c r="AK49" s="13" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AL49" s="19">
-        <v>394</v>
-      </c>
-      <c r="AM49" s="13" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
+      <c r="AK49" s="13"/>
+      <c r="AL49" s="19"/>
+      <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49"/>
-      <c r="AQ49" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR49" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS49" s="14" t="inlineStr">
-        <is>
-          <t>Lucn</t>
-        </is>
-      </c>
-      <c r="AT49" s="13" t="inlineStr">
-        <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU49" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV49" s="14" t="inlineStr">
-        <is>
-          <t>Zengchengqu Guangdongsheng 511300 CN</t>
-        </is>
-      </c>
-      <c r="AW49" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJD9ONY8MI53U</t>
-        </is>
-      </c>
+      <c r="AQ49" s="19"/>
+      <c r="AR49" s="19"/>
+      <c r="AS49" s="14"/>
+      <c r="AT49" s="13"/>
+      <c r="AU49" s="13"/>
+      <c r="AV49" s="14"/>
+      <c r="AW49" s="13"/>
       <c r="AX49" s="13"/>
-      <c r="AY49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY49" s="13"/>
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
@@ -15468,11 +15340,7 @@
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
-      <c r="BI49" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI49" s="23"/>
       <c r="BJ49" s="23"/>
       <c r="BK49" s="23"/>
       <c r="BL49" s="23"/>
@@ -15482,340 +15350,6 @@
       <c r="BP49" s="23"/>
       <c r="BQ49" s="23"/>
       <c r="BR49" s="13"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B01LX6WOFS</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>Ecozone</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>EcoZone Carpet Shampoo Solution, Deep Cleans Upholstery, Manual &amp; Machine Cleaning, Fresh Cotton Scent, 3-in-1 Plant Based St</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B01LX6WOFS</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Carpet Washers</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>22492</v>
-      </c>
-      <c r="P50" s="15">
-        <v>5850</v>
-      </c>
-      <c r="Q50" s="16">
-        <v>0.21</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Carpet Washers</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>219</v>
-      </c>
-      <c r="U50" s="16">
-        <v>-0.23</v>
-      </c>
-      <c r="V50" s="15">
-        <v>1678</v>
-      </c>
-      <c r="W50" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X50" s="15">
-        <v>762</v>
-      </c>
-      <c r="Y50" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>7.66</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="15">
-        <v>9</v>
-      </c>
-      <c r="AD50" s="19">
-        <v>902</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>1</v>
-      </c>
-      <c r="AF50" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0.0046</v>
-      </c>
-      <c r="AH50" s="20">
-        <v>3.1</v>
-      </c>
-      <c r="AI50" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2017-05-30</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>3379</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR50" s="19">
-        <v>3</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>0.43 g</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>0.43 g</t>
-        </is>
-      </c>
-      <c r="BL50" s="23" t="inlineStr">
-        <is>
-          <t>8 x 12 x 25 cm</t>
-        </is>
-      </c>
-      <c r="BM50" s="23" t="inlineStr">
-        <is>
-          <t>8.00 x 12.00 x 25.00 cm</t>
-        </is>
-      </c>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>1.06 kg</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>1.06 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>23.4 x 11.9 x 7 cm</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>23.40 x 11.90 x 7.00 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>小包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0CFV7HZHH</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Shark StainStriker Stain and Spot Cleaner, Blue PX200UK, 2 Tools, PX200UKsCompact Carpet and Upholstery Cleaner with Powerf</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0CFV7HZHH?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/719JsBbXXGL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0CFV7HZHH</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="19">
-        <v>273</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16017,181 +15551,166 @@
     <hyperlink ref="L28" r:id="rId194" tooltip="https://www.amazon.co.uk/dp/B0DPGHTW5G"/>
     <hyperlink ref="M28" r:id="rId195" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N28" r:id="rId196"/>
-    <hyperlink ref="C29" r:id="rId197" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ"/>
-    <hyperlink ref="G29" r:id="rId198" tooltip="https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0FNX6YLCJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J29" r:id="rId199" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ?psc=1"/>
-    <hyperlink ref="K29" r:id="rId200" tooltip="https://images-na.ssl-images-amazon.com/images/I/71SuXoGPIQL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId201" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ"/>
+    <hyperlink ref="C29" r:id="rId197" tooltip="https://www.amazon.co.uk/dp/B01MSJEGL8"/>
+    <hyperlink ref="G29" r:id="rId198" tooltip="https://www.amazon.co.uk/stores/RussellHobbs/page/DBC20DE0-0B1A-4442-8FF1-4D12520F0C8F?lp_asin=B01MSJEGL8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J29" r:id="rId199" tooltip="https://www.amazon.co.uk/dp/B01MSJEGL8?psc=1"/>
+    <hyperlink ref="K29" r:id="rId200" tooltip="https://images-na.ssl-images-amazon.com/images/I/61wQefXoNXL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId201" tooltip="https://www.amazon.co.uk/dp/B01MSJEGL8"/>
     <hyperlink ref="M29" r:id="rId202" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N29" r:id="rId203"/>
-    <hyperlink ref="C30" r:id="rId204" tooltip="https://www.amazon.co.uk/dp/B01MSJEGL8"/>
-    <hyperlink ref="G30" r:id="rId205" tooltip="https://www.amazon.co.uk/stores/RussellHobbs/page/DBC20DE0-0B1A-4442-8FF1-4D12520F0C8F?lp_asin=B01MSJEGL8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J30" r:id="rId206" tooltip="https://www.amazon.co.uk/dp/B01MSJEGL8?psc=1"/>
-    <hyperlink ref="K30" r:id="rId207" tooltip="https://images-na.ssl-images-amazon.com/images/I/61wQefXoNXL._AC_US600_.jpg"/>
-    <hyperlink ref="L30" r:id="rId208" tooltip="https://www.amazon.co.uk/dp/B01MSJEGL8"/>
+    <hyperlink ref="C30" r:id="rId204" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
+    <hyperlink ref="G30" r:id="rId205" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Hjh"/>
+    <hyperlink ref="J30" r:id="rId206" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1"/>
+    <hyperlink ref="K30" r:id="rId207" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_US600_.jpg"/>
+    <hyperlink ref="L30" r:id="rId208" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
     <hyperlink ref="M30" r:id="rId209" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N30" r:id="rId210"/>
-    <hyperlink ref="C31" r:id="rId211" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
-    <hyperlink ref="G31" r:id="rId212" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Hjh"/>
-    <hyperlink ref="J31" r:id="rId213" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1"/>
-    <hyperlink ref="K31" r:id="rId214" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId215" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
-    <hyperlink ref="M31" r:id="rId216" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N31" r:id="rId217"/>
-    <hyperlink ref="AW31" r:id="rId218" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UO155PK9MELH"/>
-    <hyperlink ref="C32" r:id="rId219" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M"/>
-    <hyperlink ref="G32" r:id="rId220" tooltip="https://www.amazon.co.uk/stores/OlsenSmith/page/1FA1F547-221C-40C6-BA4F-6E13B39F7CE1?lp_asin=B0GGJB2H1M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J32" r:id="rId221" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M?psc=1"/>
-    <hyperlink ref="K32" r:id="rId222" tooltip="https://images-na.ssl-images-amazon.com/images/I/719P6ABoSnL._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId223" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M"/>
-    <hyperlink ref="M32" r:id="rId224" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N32" r:id="rId225"/>
-    <hyperlink ref="AW32" r:id="rId226" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3VYMLCCHTLVWV"/>
-    <hyperlink ref="C33" r:id="rId227" tooltip="https://www.amazon.co.uk/dp/B0H8Y31Y7C"/>
-    <hyperlink ref="G33" r:id="rId228" tooltip="https://www.amazon.co.uk/stores/24-hourrapidresponse/page/2AA9E9E0-E703-4ECF-AC64-366A67AE77A7?lp_asin=B0H8Y31Y7C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J33" r:id="rId229" tooltip="https://www.amazon.co.uk/dp/B0H8Y31Y7C?psc=1"/>
-    <hyperlink ref="K33" r:id="rId230" tooltip="https://images-na.ssl-images-amazon.com/images/I/614JtpGJI8L._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId231" tooltip="https://www.amazon.co.uk/dp/B0H8Y31Y7C"/>
-    <hyperlink ref="M33" r:id="rId232" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N33" r:id="rId233"/>
-    <hyperlink ref="AW33" r:id="rId234" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABDQMGK4MGMOL"/>
-    <hyperlink ref="C34" r:id="rId235" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF"/>
-    <hyperlink ref="G34" r:id="rId236" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Domixo"/>
-    <hyperlink ref="J34" r:id="rId237" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF?psc=1"/>
-    <hyperlink ref="K34" r:id="rId238" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NkpfFNvkL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId239" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF"/>
-    <hyperlink ref="M34" r:id="rId240" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N34" r:id="rId241"/>
-    <hyperlink ref="AW34" r:id="rId242" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WYJ2QAIMP7S0"/>
-    <hyperlink ref="C35" r:id="rId243" tooltip="https://www.amazon.co.uk/dp/B0FWS2V14K"/>
-    <hyperlink ref="G35" r:id="rId244" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=ToyGem"/>
-    <hyperlink ref="J35" r:id="rId245" tooltip="https://www.amazon.co.uk/dp/B0FWS2V14K?psc=1"/>
-    <hyperlink ref="K35" r:id="rId246" tooltip="https://m.media-amazon.com/images/I/51HxyFWy+ZL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId247" tooltip="https://www.amazon.co.uk/dp/B0FWS2V14K"/>
-    <hyperlink ref="M35" r:id="rId248" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N35" r:id="rId249"/>
-    <hyperlink ref="AW35" r:id="rId250" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2F8EA95F3IAV8"/>
-    <hyperlink ref="C36" r:id="rId251" tooltip="https://www.amazon.co.uk/dp/B096KMBG8K"/>
-    <hyperlink ref="G36" r:id="rId252" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B096KMBG8K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J36" r:id="rId253" tooltip="https://www.amazon.co.uk/dp/B096KMBG8K?psc=1"/>
-    <hyperlink ref="K36" r:id="rId254" tooltip="https://m.media-amazon.com/images/I/415g5BMj1rL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId255" tooltip="https://www.amazon.co.uk/dp/B096KMBG8K"/>
-    <hyperlink ref="M36" r:id="rId256" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N36" r:id="rId257"/>
-    <hyperlink ref="AW36" r:id="rId258" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
-    <hyperlink ref="C37" r:id="rId259" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
-    <hyperlink ref="G37" r:id="rId260" tooltip="https://www.amazon.co.uk/uwant/b/ref=bl_dp_s_web_91770098031?ie=UTF8&amp;node=91770098031&amp;field-lbr_brands_browse-bin=uwant"/>
-    <hyperlink ref="J37" r:id="rId261" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1"/>
-    <hyperlink ref="K37" r:id="rId262" tooltip="https://m.media-amazon.com/images/I/41SUDAA37WL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId263" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
-    <hyperlink ref="M37" r:id="rId264" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N37" r:id="rId265"/>
-    <hyperlink ref="AW37" r:id="rId266" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17T2O4U8TIBEZ"/>
-    <hyperlink ref="C38" r:id="rId267" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B"/>
-    <hyperlink ref="G38" r:id="rId268" tooltip="https://www.amazon.co.uk/stores/Vacmaster/page/75F2E189-B394-439E-9CC9-6F4AB03DFAE5?lp_asin=B0DJMCBY4B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId269" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B?psc=1"/>
-    <hyperlink ref="K38" r:id="rId270" tooltip="https://m.media-amazon.com/images/I/41PLSFp59LL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId271" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B"/>
+    <hyperlink ref="AW30" r:id="rId211" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UO155PK9MELH"/>
+    <hyperlink ref="C31" r:id="rId212" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M"/>
+    <hyperlink ref="G31" r:id="rId213" tooltip="https://www.amazon.co.uk/stores/OlsenSmith/page/1FA1F547-221C-40C6-BA4F-6E13B39F7CE1?lp_asin=B0GGJB2H1M&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J31" r:id="rId214" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M?psc=1"/>
+    <hyperlink ref="K31" r:id="rId215" tooltip="https://images-na.ssl-images-amazon.com/images/I/719P6ABoSnL._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId216" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M"/>
+    <hyperlink ref="M31" r:id="rId217" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N31" r:id="rId218"/>
+    <hyperlink ref="AW31" r:id="rId219" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3VYMLCCHTLVWV"/>
+    <hyperlink ref="C32" r:id="rId220" tooltip="https://www.amazon.co.uk/dp/B0H8Y31Y7C"/>
+    <hyperlink ref="G32" r:id="rId221" tooltip="https://www.amazon.co.uk/stores/24-hourrapidresponse/page/2AA9E9E0-E703-4ECF-AC64-366A67AE77A7?lp_asin=B0H8Y31Y7C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J32" r:id="rId222" tooltip="https://www.amazon.co.uk/dp/B0H8Y31Y7C?psc=1"/>
+    <hyperlink ref="K32" r:id="rId223" tooltip="https://images-na.ssl-images-amazon.com/images/I/614JtpGJI8L._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId224" tooltip="https://www.amazon.co.uk/dp/B0H8Y31Y7C"/>
+    <hyperlink ref="M32" r:id="rId225" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N32" r:id="rId226"/>
+    <hyperlink ref="AW32" r:id="rId227" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABDQMGK4MGMOL"/>
+    <hyperlink ref="C33" r:id="rId228" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF"/>
+    <hyperlink ref="G33" r:id="rId229" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Domixo"/>
+    <hyperlink ref="J33" r:id="rId230" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF?psc=1"/>
+    <hyperlink ref="K33" r:id="rId231" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NkpfFNvkL._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId232" tooltip="https://www.amazon.co.uk/dp/B0FXGBT4LF"/>
+    <hyperlink ref="M33" r:id="rId233" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N33" r:id="rId234"/>
+    <hyperlink ref="AW33" r:id="rId235" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WYJ2QAIMP7S0"/>
+    <hyperlink ref="C34" r:id="rId236" tooltip="https://www.amazon.co.uk/dp/B0FWS2V14K"/>
+    <hyperlink ref="G34" r:id="rId237" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=ToyGem"/>
+    <hyperlink ref="J34" r:id="rId238" tooltip="https://www.amazon.co.uk/dp/B0FWS2V14K?psc=1"/>
+    <hyperlink ref="K34" r:id="rId239" tooltip="https://m.media-amazon.com/images/I/51HxyFWy+ZL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId240" tooltip="https://www.amazon.co.uk/dp/B0FWS2V14K"/>
+    <hyperlink ref="M34" r:id="rId241" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N34" r:id="rId242"/>
+    <hyperlink ref="AW34" r:id="rId243" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2F8EA95F3IAV8"/>
+    <hyperlink ref="C35" r:id="rId244" tooltip="https://www.amazon.co.uk/dp/B096KMBG8K"/>
+    <hyperlink ref="G35" r:id="rId245" tooltip="https://www.amazon.co.uk/stores/VYTRONIX/page/0488BBB4-7668-4BD9-83CC-3C85540B802C?lp_asin=B096KMBG8K&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J35" r:id="rId246" tooltip="https://www.amazon.co.uk/dp/B096KMBG8K?psc=1"/>
+    <hyperlink ref="K35" r:id="rId247" tooltip="https://m.media-amazon.com/images/I/415g5BMj1rL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId248" tooltip="https://www.amazon.co.uk/dp/B096KMBG8K"/>
+    <hyperlink ref="M35" r:id="rId249" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N35" r:id="rId250"/>
+    <hyperlink ref="AW35" r:id="rId251" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1ZNUHI65TJJP2"/>
+    <hyperlink ref="C36" r:id="rId252" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
+    <hyperlink ref="G36" r:id="rId253" tooltip="https://www.amazon.co.uk/uwant/b/ref=bl_dp_s_web_91770098031?ie=UTF8&amp;node=91770098031&amp;field-lbr_brands_browse-bin=uwant"/>
+    <hyperlink ref="J36" r:id="rId254" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1"/>
+    <hyperlink ref="K36" r:id="rId255" tooltip="https://m.media-amazon.com/images/I/41SUDAA37WL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId256" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
+    <hyperlink ref="M36" r:id="rId257" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N36" r:id="rId258"/>
+    <hyperlink ref="AW36" r:id="rId259" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A17T2O4U8TIBEZ"/>
+    <hyperlink ref="C37" r:id="rId260" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B"/>
+    <hyperlink ref="G37" r:id="rId261" tooltip="https://www.amazon.co.uk/stores/Vacmaster/page/75F2E189-B394-439E-9CC9-6F4AB03DFAE5?lp_asin=B0DJMCBY4B&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId262" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B?psc=1"/>
+    <hyperlink ref="K37" r:id="rId263" tooltip="https://m.media-amazon.com/images/I/41PLSFp59LL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId264" tooltip="https://www.amazon.co.uk/dp/B0DJMCBY4B"/>
+    <hyperlink ref="M37" r:id="rId265" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N37" r:id="rId266"/>
+    <hyperlink ref="C38" r:id="rId267" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ"/>
+    <hyperlink ref="G38" r:id="rId268" tooltip="https://www.amazon.co.uk/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/B7CD0F54-C752-439A-AD08-CA062A6946FF?lp_asin=B0GDDKS6ZJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId269" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ?psc=1"/>
+    <hyperlink ref="K38" r:id="rId270" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ppKXUCKdL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId271" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ"/>
     <hyperlink ref="M38" r:id="rId272" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N38" r:id="rId273"/>
-    <hyperlink ref="C39" r:id="rId274" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ"/>
-    <hyperlink ref="G39" r:id="rId275" tooltip="https://www.amazon.co.uk/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/B7CD0F54-C752-439A-AD08-CA062A6946FF?lp_asin=B0GDDKS6ZJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId276" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ?psc=1"/>
-    <hyperlink ref="K39" r:id="rId277" tooltip="https://images-na.ssl-images-amazon.com/images/I/71ppKXUCKdL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId278" tooltip="https://www.amazon.co.uk/dp/B0GDDKS6ZJ"/>
-    <hyperlink ref="M39" r:id="rId279" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N39" r:id="rId280"/>
-    <hyperlink ref="AW39" r:id="rId281" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGEBNOEX5B7LS"/>
-    <hyperlink ref="C40" r:id="rId282" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR"/>
-    <hyperlink ref="G40" r:id="rId283" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId284" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR?psc=1"/>
-    <hyperlink ref="K40" r:id="rId285" tooltip="https://m.media-amazon.com/images/I/31LC0CHQzZL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId286" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR"/>
-    <hyperlink ref="M40" r:id="rId287" tooltip="https://www.amazon.co.uk/b?node=27348822031"/>
-    <hyperlink ref="N40" r:id="rId288"/>
-    <hyperlink ref="AW40" r:id="rId289" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKGAA3WULFPOP"/>
-    <hyperlink ref="C41" r:id="rId290" tooltip="https://www.amazon.co.uk/dp/B0DMTFH97X"/>
-    <hyperlink ref="G41" r:id="rId291" tooltip="https://www.amazon.co.uk/Abode/b/ref=bl_dp_s_web_61386520031?ie=UTF8&amp;node=61386520031&amp;field-lbr_brands_browse-bin=Abode"/>
-    <hyperlink ref="J41" r:id="rId292" tooltip="https://www.amazon.co.uk/dp/B0DMTFH97X?psc=1"/>
-    <hyperlink ref="K41" r:id="rId293" tooltip="https://images-na.ssl-images-amazon.com/images/I/71d09y-wiwL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId294" tooltip="https://www.amazon.co.uk/dp/B0DMTFH97X"/>
-    <hyperlink ref="M41" r:id="rId295" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N41" r:id="rId296"/>
-    <hyperlink ref="AW41" r:id="rId297" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A34BWCJVHPX7M7"/>
-    <hyperlink ref="C42" r:id="rId298" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
-    <hyperlink ref="G42" r:id="rId299" tooltip="https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J42" r:id="rId300" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T?psc=1"/>
-    <hyperlink ref="K42" r:id="rId301" tooltip="https://images-na.ssl-images-amazon.com/images/I/71l-bqPqPSL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId302" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
+    <hyperlink ref="AW38" r:id="rId274" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGEBNOEX5B7LS"/>
+    <hyperlink ref="C39" r:id="rId275" tooltip="https://www.amazon.co.uk/dp/B0DMTFH97X"/>
+    <hyperlink ref="G39" r:id="rId276" tooltip="https://www.amazon.co.uk/Abode/b/ref=bl_dp_s_web_61386520031?ie=UTF8&amp;node=61386520031&amp;field-lbr_brands_browse-bin=Abode"/>
+    <hyperlink ref="J39" r:id="rId277" tooltip="https://www.amazon.co.uk/dp/B0DMTFH97X?psc=1"/>
+    <hyperlink ref="K39" r:id="rId278" tooltip="https://images-na.ssl-images-amazon.com/images/I/71d09y-wiwL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId279" tooltip="https://www.amazon.co.uk/dp/B0DMTFH97X"/>
+    <hyperlink ref="M39" r:id="rId280" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N39" r:id="rId281"/>
+    <hyperlink ref="AW39" r:id="rId282" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A34BWCJVHPX7M7"/>
+    <hyperlink ref="C40" r:id="rId283" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
+    <hyperlink ref="G40" r:id="rId284" tooltip="https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J40" r:id="rId285" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T?psc=1"/>
+    <hyperlink ref="K40" r:id="rId286" tooltip="https://images-na.ssl-images-amazon.com/images/I/71l-bqPqPSL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId287" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
+    <hyperlink ref="M40" r:id="rId288" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N40" r:id="rId289"/>
+    <hyperlink ref="AW40" r:id="rId290" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W"/>
+    <hyperlink ref="C41" r:id="rId291" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
+    <hyperlink ref="G41" r:id="rId292" tooltip="https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J41" r:id="rId293" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1"/>
+    <hyperlink ref="K41" r:id="rId294" tooltip="https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId295" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
+    <hyperlink ref="M41" r:id="rId296" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N41" r:id="rId297"/>
+    <hyperlink ref="C42" r:id="rId298" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
+    <hyperlink ref="G42" r:id="rId299" tooltip="https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0FZBSDZ26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J42" r:id="rId300" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1"/>
+    <hyperlink ref="K42" r:id="rId301" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Dl6k2D2FL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId302" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
     <hyperlink ref="M42" r:id="rId303" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N42" r:id="rId304"/>
-    <hyperlink ref="AW42" r:id="rId305" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W"/>
-    <hyperlink ref="C43" r:id="rId306" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
-    <hyperlink ref="G43" r:id="rId307" tooltip="https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId308" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1"/>
-    <hyperlink ref="K43" r:id="rId309" tooltip="https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId310" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
+    <hyperlink ref="AW42" r:id="rId305" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6"/>
+    <hyperlink ref="C43" r:id="rId306" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57"/>
+    <hyperlink ref="G43" r:id="rId307" tooltip="https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09JSVWX57&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J43" r:id="rId308" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57?psc=1"/>
+    <hyperlink ref="K43" r:id="rId309" tooltip="https://m.media-amazon.com/images/I/41uf-z8AXOL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId310" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57"/>
     <hyperlink ref="M43" r:id="rId311" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N43" r:id="rId312"/>
-    <hyperlink ref="C44" r:id="rId313" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
-    <hyperlink ref="G44" r:id="rId314" tooltip="https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0FZBSDZ26&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId315" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1"/>
-    <hyperlink ref="K44" r:id="rId316" tooltip="https://images-na.ssl-images-amazon.com/images/I/71Dl6k2D2FL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
+    <hyperlink ref="C44" r:id="rId313" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
+    <hyperlink ref="G44" r:id="rId314" tooltip="https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J44" r:id="rId315" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1"/>
+    <hyperlink ref="K44" r:id="rId316" tooltip="https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
     <hyperlink ref="M44" r:id="rId318" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N44" r:id="rId319"/>
-    <hyperlink ref="AW44" r:id="rId320" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6"/>
-    <hyperlink ref="C45" r:id="rId321" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57"/>
-    <hyperlink ref="G45" r:id="rId322" tooltip="https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09JSVWX57&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId323" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57?psc=1"/>
-    <hyperlink ref="K45" r:id="rId324" tooltip="https://m.media-amazon.com/images/I/41uf-z8AXOL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId325" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57"/>
-    <hyperlink ref="M45" r:id="rId326" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N45" r:id="rId327"/>
-    <hyperlink ref="C46" r:id="rId328" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
-    <hyperlink ref="G46" r:id="rId329" tooltip="https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId330" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1"/>
-    <hyperlink ref="K46" r:id="rId331" tooltip="https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId332" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
-    <hyperlink ref="M46" r:id="rId333" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N46" r:id="rId334"/>
-    <hyperlink ref="C47" r:id="rId335" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5"/>
-    <hyperlink ref="G47" r:id="rId336" tooltip="https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0H6KDXVQ5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId337" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5?psc=1"/>
-    <hyperlink ref="K47" r:id="rId338" tooltip="https://m.media-amazon.com/images/I/31R6lJG42+L._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId339" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5"/>
+    <hyperlink ref="C45" r:id="rId320" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5"/>
+    <hyperlink ref="G45" r:id="rId321" tooltip="https://www.amazon.co.uk/stores/Shark/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0H6KDXVQ5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId322" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5?psc=1"/>
+    <hyperlink ref="K45" r:id="rId323" tooltip="https://m.media-amazon.com/images/I/31R6lJG42+L._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId324" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5"/>
+    <hyperlink ref="M45" r:id="rId325" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N45" r:id="rId326"/>
+    <hyperlink ref="C46" r:id="rId327" tooltip="https://www.amazon.co.uk/dp/B08GSPYJ68"/>
+    <hyperlink ref="G46" r:id="rId328" tooltip="https://www.amazon.co.uk/stores/Ewbank/page/379635B0-DB01-48B5-9749-216DB75EB5AC?lp_asin=B08GSPYJ68&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J46" r:id="rId329" tooltip="https://www.amazon.co.uk/dp/B08GSPYJ68?psc=1"/>
+    <hyperlink ref="K46" r:id="rId330" tooltip="https://images-na.ssl-images-amazon.com/images/I/41CrruJ27DL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId331" tooltip="https://www.amazon.co.uk/dp/B08GSPYJ68"/>
+    <hyperlink ref="M46" r:id="rId332" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N46" r:id="rId333"/>
+    <hyperlink ref="AW46" r:id="rId334" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29F1JIJWJQSEI"/>
+    <hyperlink ref="C47" r:id="rId335" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
+    <hyperlink ref="G47" r:id="rId336" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=VickyHome"/>
+    <hyperlink ref="J47" r:id="rId337" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1"/>
+    <hyperlink ref="K47" r:id="rId338" tooltip="https://m.media-amazon.com/images/I/41G0usLZmPL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId339" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
     <hyperlink ref="M47" r:id="rId340" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N47" r:id="rId341"/>
-    <hyperlink ref="C48" r:id="rId342" tooltip="https://www.amazon.co.uk/dp/B08GSPYJ68"/>
-    <hyperlink ref="G48" r:id="rId343" tooltip="https://www.amazon.co.uk/stores/Ewbank/page/379635B0-DB01-48B5-9749-216DB75EB5AC?lp_asin=B08GSPYJ68&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J48" r:id="rId344" tooltip="https://www.amazon.co.uk/dp/B08GSPYJ68?psc=1"/>
-    <hyperlink ref="K48" r:id="rId345" tooltip="https://images-na.ssl-images-amazon.com/images/I/41CrruJ27DL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId346" tooltip="https://www.amazon.co.uk/dp/B08GSPYJ68"/>
-    <hyperlink ref="M48" r:id="rId347" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N48" r:id="rId348"/>
-    <hyperlink ref="AW48" r:id="rId349" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A29F1JIJWJQSEI"/>
-    <hyperlink ref="C49" r:id="rId350" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
-    <hyperlink ref="G49" r:id="rId351" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=VickyHome"/>
-    <hyperlink ref="J49" r:id="rId352" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1"/>
-    <hyperlink ref="K49" r:id="rId353" tooltip="https://m.media-amazon.com/images/I/41G0usLZmPL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId354" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
-    <hyperlink ref="M49" r:id="rId355" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N49" r:id="rId356"/>
-    <hyperlink ref="AW49" r:id="rId357" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJD9ONY8MI53U"/>
-    <hyperlink ref="C50" r:id="rId358" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
-    <hyperlink ref="G50" r:id="rId359" tooltip="https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId360" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1"/>
-    <hyperlink ref="K50" r:id="rId361" tooltip="https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId362" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
-    <hyperlink ref="M50" r:id="rId363" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N50" r:id="rId364"/>
-    <hyperlink ref="C51" r:id="rId365" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH"/>
-    <hyperlink ref="G51" r:id="rId366" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J51" r:id="rId367" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH?psc=1"/>
-    <hyperlink ref="K51" r:id="rId368" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719JsBbXXGL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId369" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH"/>
+    <hyperlink ref="AW47" r:id="rId342" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJD9ONY8MI53U"/>
+    <hyperlink ref="C48" r:id="rId343" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
+    <hyperlink ref="G48" r:id="rId344" tooltip="https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId345" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1"/>
+    <hyperlink ref="K48" r:id="rId346" tooltip="https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId347" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
+    <hyperlink ref="M48" r:id="rId348" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N48" r:id="rId349"/>
+    <hyperlink ref="C49" r:id="rId350" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH"/>
+    <hyperlink ref="G49" r:id="rId351" tooltip="https://www.amazon.co.ukundefined"/>
+    <hyperlink ref="J49" r:id="rId352" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH?psc=1"/>
+    <hyperlink ref="K49" r:id="rId353" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719JsBbXXGL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId354" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH"/>
   </hyperlinks>
-  <drawing r:id="rId370"/>
+  <drawing r:id="rId355"/>
 </worksheet>
 </file>
 
@@ -16261,7 +15780,7 @@
         <v>100.81623954680335</v>
       </c>
       <c r="G2" s="22">
-        <v>0.48018134715025906</v>
+        <v>0.5040794125645907</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16271,18 +15790,18 @@
         </is>
       </c>
       <c r="B3" s="15">
-        <v>4964</v>
+        <v>4090</v>
       </c>
       <c r="C3" s="15">
-        <v>679775</v>
+        <v>653564</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="20">
-        <v>136.94097502014503</v>
+        <v>159.7955990220049</v>
       </c>
       <c r="G3" s="22">
-        <v>0.12860103626943006</v>
+        <v>0.1112319825945064</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16292,18 +15811,18 @@
         </is>
       </c>
       <c r="B4" s="15">
-        <v>5025</v>
+        <v>4069</v>
       </c>
       <c r="C4" s="15">
-        <v>393365</v>
+        <v>383996</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="20">
-        <v>78.281592039801</v>
+        <v>94.37109855001229</v>
       </c>
       <c r="G4" s="22">
-        <v>0.13018134715025906</v>
+        <v>0.1106608648354637</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16324,7 +15843,7 @@
         <v>47.493073593073596</v>
       </c>
       <c r="G5" s="22">
-        <v>0.05984455958549223</v>
+        <v>0.06282295349469677</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16345,7 +15864,7 @@
         <v>290.0</v>
       </c>
       <c r="G6" s="22">
-        <v>0.009430051813471502</v>
+        <v>0.009899374490073429</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16366,7 +15885,7 @@
         <v>59.990311418685124</v>
       </c>
       <c r="G7" s="22">
-        <v>0.037435233160621764</v>
+        <v>0.0392983410388904</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16387,7 +15906,7 @@
         <v>53.21178225205071</v>
       </c>
       <c r="G8" s="22">
-        <v>0.034740932642487045</v>
+        <v>0.03646994832744085</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16408,7 +15927,7 @@
         <v>72.98959537572254</v>
       </c>
       <c r="G9" s="22">
-        <v>0.022409326424870465</v>
+        <v>0.023524612455806365</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16429,7 +15948,7 @@
         <v>79.98876404494382</v>
       </c>
       <c r="G10" s="22">
-        <v>0.00922279792746114</v>
+        <v>0.009681805819961925</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16450,7 +15969,7 @@
         <v>68.0</v>
       </c>
       <c r="G11" s="22">
-        <v>0.009740932642487047</v>
+        <v>0.010225727495240686</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16471,7 +15990,7 @@
         <v>56.98870056497175</v>
       </c>
       <c r="G12" s="22">
-        <v>0.009170984455958549</v>
+        <v>0.009627413652434049</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16492,7 +16011,7 @@
         <v>56.99101796407186</v>
       </c>
       <c r="G13" s="22">
-        <v>0.008652849740932642</v>
+        <v>0.00908349197715529</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16513,7 +16032,7 @@
         <v>66.47940074906367</v>
       </c>
       <c r="G14" s="22">
-        <v>0.006917098445595855</v>
+        <v>0.007261354364971444</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16534,7 +16053,7 @@
         <v>69.98974358974358</v>
       </c>
       <c r="G15" s="22">
-        <v>0.005051813471502591</v>
+        <v>0.005303236333967908</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16555,7 +16074,7 @@
         <v>69.9888888888889</v>
       </c>
       <c r="G16" s="22">
-        <v>0.00466321243523316</v>
+        <v>0.004895295077508839</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16576,7 +16095,7 @@
         <v>99.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.002901554404145078</v>
+        <v>0.003045961381561055</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16597,7 +16116,7 @@
         <v>59.98780487804878</v>
       </c>
       <c r="G18" s="22">
-        <v>0.004248704663212435</v>
+        <v>0.004460157737285831</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16618,7 +16137,7 @@
         <v>79.99159663865547</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0030829015544041453</v>
+        <v>0.003236333967908621</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16639,7 +16158,7 @@
         <v>44.989583333333336</v>
       </c>
       <c r="G20" s="22">
-        <v>0.004974093264248704</v>
+        <v>0.005221648082676095</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16660,7 +16179,7 @@
         <v>49.98809523809524</v>
       </c>
       <c r="G21" s="22">
-        <v>0.004352331606217617</v>
+        <v>0.004568942072341583</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16681,7 +16200,7 @@
         <v>42.4875</v>
       </c>
       <c r="G22" s="22">
-        <v>0.004145077720207254</v>
+        <v>0.004351373402230079</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16702,7 +16221,7 @@
         <v>59.990990990990994</v>
       </c>
       <c r="G23" s="22">
-        <v>0.0028756476683937824</v>
+        <v>0.0030187652977971173</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16723,7 +16242,7 @@
         <v>59.99038461538461</v>
       </c>
       <c r="G24" s="22">
-        <v>0.002694300518134715</v>
+        <v>0.002828392711449551</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16744,7 +16263,7 @@
         <v>39.991379310344826</v>
       </c>
       <c r="G25" s="22">
-        <v>0.003005181347150259</v>
+        <v>0.003154745716616807</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16765,7 +16284,7 @@
         <v>26.992805755395683</v>
       </c>
       <c r="G26" s="22">
-        <v>0.003601036269430052</v>
+        <v>0.003780255643187381</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16786,7 +16305,7 @@
         <v>35.56470588235294</v>
       </c>
       <c r="G27" s="22">
-        <v>0.0022020725388601035</v>
+        <v>0.0023116671199347296</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16807,7 +16326,7 @@
         <v>7.662100456621005</v>
       </c>
       <c r="G28" s="22">
-        <v>0.005673575129533679</v>
+        <v>0.0059559423443024204</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16837,7 +16356,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -16890,18 +16409,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>26908</v>
+        <v>26034</v>
       </c>
       <c r="C2" s="15">
-        <v>2921503</v>
+        <v>2895292</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>108.5737698825628</v>
+        <v>111.21195359913959</v>
       </c>
       <c r="G2" s="22">
-        <v>0.6970984455958549</v>
+        <v>0.7080228447103617</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16922,7 +16441,7 @@
         <v>190.0</v>
       </c>
       <c r="G3" s="22">
-        <v>0.02300518134715026</v>
+        <v>0.02415012238237694</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16943,7 +16462,7 @@
         <v>47.493073593073596</v>
       </c>
       <c r="G4" s="22">
-        <v>0.05984455958549223</v>
+        <v>0.06282295349469677</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16964,7 +16483,7 @@
         <v>59.990311418685124</v>
       </c>
       <c r="G5" s="22">
-        <v>0.037435233160621764</v>
+        <v>0.0392983410388904</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -16985,7 +16504,7 @@
         <v>53.21178225205071</v>
       </c>
       <c r="G6" s="22">
-        <v>0.034740932642487045</v>
+        <v>0.03646994832744085</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17006,7 +16525,7 @@
         <v>72.98959537572254</v>
       </c>
       <c r="G7" s="22">
-        <v>0.022409326424870465</v>
+        <v>0.023524612455806365</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17027,7 +16546,7 @@
         <v>18.990190067443287</v>
       </c>
       <c r="G8" s="22">
-        <v>0.042253886010362694</v>
+        <v>0.04435681261898287</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17048,7 +16567,7 @@
         <v>56.98870056497175</v>
       </c>
       <c r="G9" s="22">
-        <v>0.009170984455958549</v>
+        <v>0.009627413652434049</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17069,7 +16588,7 @@
         <v>56.99101796407186</v>
       </c>
       <c r="G10" s="22">
-        <v>0.008652849740932642</v>
+        <v>0.00908349197715529</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17090,7 +16609,7 @@
         <v>66.47940074906367</v>
       </c>
       <c r="G11" s="22">
-        <v>0.006917098445595855</v>
+        <v>0.007261354364971444</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17111,7 +16630,7 @@
         <v>69.98974358974358</v>
       </c>
       <c r="G12" s="22">
-        <v>0.005051813471502591</v>
+        <v>0.005303236333967908</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17132,7 +16651,7 @@
         <v>69.9888888888889</v>
       </c>
       <c r="G13" s="22">
-        <v>0.00466321243523316</v>
+        <v>0.004895295077508839</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17153,7 +16672,7 @@
         <v>99.0</v>
       </c>
       <c r="G14" s="22">
-        <v>0.002901554404145078</v>
+        <v>0.003045961381561055</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -17174,151 +16693,130 @@
         <v>79.99159663865547</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0030829015544041453</v>
+        <v>0.003236333967908621</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Reliapart</t>
+          <t>Electrical Shop</t>
         </is>
       </c>
       <c r="B16" s="15">
-        <v>956</v>
+        <v>192</v>
       </c>
       <c r="C16" s="15">
-        <v>9369</v>
+        <v>8638</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="20">
-        <v>9.80020920502092</v>
+        <v>44.989583333333336</v>
       </c>
       <c r="G16" s="22">
-        <v>0.024766839378238342</v>
+        <v>0.005221648082676095</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Electrical Shop</t>
+          <t>homeofbrands</t>
         </is>
       </c>
       <c r="B17" s="15">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="C17" s="15">
-        <v>8638</v>
+        <v>8398</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="20">
-        <v>44.989583333333336</v>
+        <v>49.98809523809524</v>
       </c>
       <c r="G17" s="22">
-        <v>0.004974093264248704</v>
+        <v>0.004568942072341583</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>homeofbrands</t>
+          <t>VonHaus UK</t>
         </is>
       </c>
       <c r="B18" s="15">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="C18" s="15">
-        <v>8398</v>
+        <v>6659</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="20">
-        <v>49.98809523809524</v>
+        <v>59.990990990990994</v>
       </c>
       <c r="G18" s="22">
-        <v>0.004352331606217617</v>
+        <v>0.0030187652977971173</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>VonHaus UK</t>
+          <t>Go Shop Direct</t>
         </is>
       </c>
       <c r="B19" s="15">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C19" s="15">
-        <v>6659</v>
+        <v>3752</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15"/>
       <c r="F19" s="20">
-        <v>59.990990990990994</v>
+        <v>26.992805755395683</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0028756476683937824</v>
+        <v>0.003780255643187381</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Go Shop Direct</t>
+          <t>Lucn</t>
         </is>
       </c>
       <c r="B20" s="15">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="C20" s="15">
-        <v>3752</v>
+        <v>3023</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15"/>
       <c r="F20" s="20">
-        <v>26.992805755395683</v>
+        <v>35.56470588235294</v>
       </c>
       <c r="G20" s="22">
-        <v>0.003601036269430052</v>
+        <v>0.0023116671199347296</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Lucn</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B21" s="15">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="C21" s="15">
-        <v>3023</v>
+        <v>0</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
-      <c r="F21" s="20">
-        <v>35.56470588235294</v>
-      </c>
+      <c r="F21" s="20"/>
       <c r="G21" s="22">
-        <v>0.0022020725388601035</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B22" s="15">
-        <v>0</v>
-      </c>
-      <c r="C22" s="15">
-        <v>0</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="22">
         <v>0.0</v>
       </c>
     </row>
